--- a/data/pronostici/TOTOMONDIALE2026_Salvatore_Scala.xlsx
+++ b/data/pronostici/TOTOMONDIALE2026_Salvatore_Scala.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.castiello\Documents\totomondiale\data\pronostici\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FA2BF2-0C3D-4145-9C15-E82C14AEC53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Riepilogo di esportazione" sheetId="1" r:id="rId4"/>
-    <sheet name="REGOLAMENTO" sheetId="2" r:id="rId5"/>
-    <sheet name="TABELLONE" sheetId="3" r:id="rId6"/>
-    <sheet name="Gironi - Tabella pivot2" sheetId="4" r:id="rId7"/>
-    <sheet name="Gironi - Tabella 1" sheetId="5" r:id="rId8"/>
+    <sheet name="Riepilogo di esportazione" sheetId="1" r:id="rId1"/>
+    <sheet name="REGOLAMENTO" sheetId="2" r:id="rId2"/>
+    <sheet name="TABELLONE" sheetId="3" r:id="rId3"/>
+    <sheet name="Gironi - Tabella pivot2" sheetId="4" r:id="rId4"/>
+    <sheet name="Gironi - Tabella 1" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="309">
   <si>
     <t>Questo documento è stato esportato da Numbers. Tutte le tabelle sono state convertite in un foglio di lavoro di Excel. Tutti gli altri oggetti di ciascun foglio di Numbers sono stati collocati in fogli di lavoro separati. Nota che i calcoli delle formule potrebbero differire in Excel.</t>
   </si>
@@ -950,12 +959,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="d-m"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -972,41 +980,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <u/>
       <sz val="12"/>
       <color indexed="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color indexed="12"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
+      <i/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="18"/>
       <color indexed="8"/>
       <name val="Bookman Old Style"/>
@@ -1017,7 +1015,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -1598,9 +1596,7 @@
       <left style="thin">
         <color indexed="22"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="22"/>
       </top>
@@ -1610,9 +1606,7 @@
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color indexed="8"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="23"/>
       </right>
@@ -1628,21 +1622,15 @@
       <left style="thin">
         <color indexed="22"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="13"/>
       </top>
-      <bottom>
-        <color indexed="8"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color indexed="8"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="24"/>
       </right>
@@ -1655,9 +1643,7 @@
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color indexed="8"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="24"/>
       </right>
@@ -1673,12 +1659,8 @@
       <left style="thin">
         <color indexed="22"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
-      <top>
-        <color indexed="8"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="24"/>
       </bottom>
@@ -1688,21 +1670,15 @@
       <left style="thin">
         <color indexed="22"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="24"/>
       </top>
-      <bottom>
-        <color indexed="8"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color indexed="8"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="24"/>
       </right>
@@ -1718,12 +1694,8 @@
       <left style="thin">
         <color indexed="22"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
-      <top>
-        <color indexed="8"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="13"/>
       </bottom>
@@ -1733,9 +1705,7 @@
       <left style="thin">
         <color indexed="22"/>
       </left>
-      <right>
-        <color indexed="8"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="13"/>
       </top>
@@ -1824,427 +1794,395 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="141">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="14" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="14" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="16" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="7" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="10" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="10" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="11" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="11" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="10" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="34" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="12" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="12" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="12" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="11" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="37" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="38" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="11" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="41" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="13" borderId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="13" borderId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="46" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="14" borderId="47" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="14" borderId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="52" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="52" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="53" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="54" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="55" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="56" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="54" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="54" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="57" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="17">
     <dxf>
       <font>
-        <color rgb="ff000000"/>
+        <b/>
+        <color rgb="FF000000"/>
       </font>
       <border>
         <left style="thin">
@@ -2254,24 +2192,367 @@
           <color indexed="22"/>
         </right>
         <top style="thin">
+          <color indexed="13"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="28"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="28"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="28"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="28"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="28"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="28"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="28"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="25"/>
+        </left>
+        <right style="thin">
+          <color indexed="25"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="25"/>
+        </left>
+        <right style="thin">
+          <color indexed="25"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="25"/>
+        </left>
+        <right style="thin">
+          <color indexed="25"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
+          <color indexed="24"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="24"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
+          <color indexed="24"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="24"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
+          <color indexed="24"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="24"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="18"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
           <color indexed="22"/>
         </top>
         <bottom style="thin">
           <color indexed="22"/>
         </bottom>
-        <diagonal/>
-        <vertical style="thin">
-          <color indexed="26"/>
-        </vertical>
+        <vertical/>
         <horizontal style="thin">
-          <color indexed="26"/>
+          <color indexed="25"/>
         </horizontal>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color rgb="ffffffff"/>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="18"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
+          <color indexed="22"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="22"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color indexed="25"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="23"/>
+        </left>
+        <right style="thin">
+          <color indexed="23"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color indexed="13"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="23"/>
+        </left>
+        <right style="thin">
+          <color indexed="23"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color indexed="13"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="23"/>
+        </left>
+        <right style="thin">
+          <color indexed="23"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color indexed="13"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -2292,160 +2573,15 @@
         <bottom style="thin">
           <color indexed="13"/>
         </bottom>
-        <diagonal/>
         <vertical style="thin">
           <color indexed="22"/>
         </vertical>
-        <horizontal>
-          <color indexed="22"/>
-        </horizontal>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color rgb="ffffffff"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="21"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="23"/>
-        </left>
-        <right style="thin">
-          <color indexed="23"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color indexed="13"/>
-        </bottom>
-        <diagonal/>
-        <vertical style="thin">
-          <color indexed="23"/>
-        </vertical>
-        <horizontal>
-          <color indexed="8"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="ff000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="18"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="22"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top style="thin">
-          <color indexed="22"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="22"/>
-        </bottom>
-        <diagonal/>
-        <vertical>
-          <color indexed="25"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="25"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="ff000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="22"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <diagonal/>
-        <vertical>
-          <color indexed="25"/>
-        </vertical>
-        <horizontal>
-          <color indexed="8"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff000000"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="25"/>
-        </left>
-        <right style="thin">
-          <color indexed="25"/>
-        </right>
-        <top/>
-        <bottom/>
-        <diagonal/>
-        <vertical style="thin">
-          <color indexed="23"/>
-        </vertical>
-        <horizontal>
-          <color indexed="8"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="28"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="28"/>
-        </bottom>
-        <diagonal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="ff000000"/>
+        <color rgb="FF000000"/>
       </font>
       <border>
         <left style="thin">
@@ -2455,80 +2591,122 @@
           <color indexed="22"/>
         </right>
         <top style="thin">
-          <color indexed="13"/>
+          <color indexed="22"/>
         </top>
         <bottom style="thin">
-          <color indexed="28"/>
+          <color indexed="22"/>
         </bottom>
-        <diagonal/>
-        <vertical>
-          <color indexed="27"/>
+        <vertical style="thin">
+          <color indexed="26"/>
         </vertical>
-        <horizontal>
-          <color indexed="22"/>
+        <horizontal style="thin">
+          <color indexed="26"/>
         </horizontal>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="PivotStyleCustom01">
-      <tableStyleElement type="wholeTable" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="1"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="2"/>
-      <tableStyleElement type="secondColumnSubheading" dxfId="2"/>
-      <tableStyleElement type="thirdColumnSubheading" dxfId="2"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="4"/>
-      <tableStyleElement type="thirdRowSubheading" dxfId="4"/>
-      <tableStyleElement type="firstSubtotalColumn" dxfId="5"/>
+    <tableStyle name="PivotStyleCustom01" count="17" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="0"/>
+      <tableStyleElement type="firstColumn" dxfId="11"/>
+      <tableStyleElement type="lastColumn" dxfId="10"/>
+      <tableStyleElement type="firstSubtotalColumn" dxfId="6"/>
       <tableStyleElement type="secondSubtotalColumn" dxfId="5"/>
-      <tableStyleElement type="thirdSubtotalColumn" dxfId="5"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="thirdSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="7"/>
+      <tableStyleElement type="thirdSubtotalColumn" dxfId="4"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="3"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="2"/>
+      <tableStyleElement type="thirdSubtotalRow" dxfId="1"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="14"/>
+      <tableStyleElement type="secondColumnSubheading" dxfId="13"/>
+      <tableStyleElement type="thirdColumnSubheading" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="9"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="8"/>
+      <tableStyleElement type="thirdRowSubheading" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff5e88b1"/>
-      <rgbColor rgb="ffeef3f4"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ff335593"/>
-      <rgbColor rgb="ffdeeaf6"/>
-      <rgbColor rgb="ffbfbfbf"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffd9e2f3"/>
-      <rgbColor rgb="fffbe4d5"/>
-      <rgbColor rgb="ffe2eeda"/>
-      <rgbColor rgb="ff4472c4"/>
-      <rgbColor rgb="ff99aac9"/>
-      <rgbColor rgb="ffb4c6e7"/>
-      <rgbColor rgb="ffa3aab6"/>
-      <rgbColor rgb="ffd1d4da"/>
-      <rgbColor rgb="ffc6d4ed"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF5E88B1"/>
+      <rgbColor rgb="FFEEF3F4"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FF335593"/>
+      <rgbColor rgb="FFDEEAF6"/>
+      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FFD9E2F3"/>
+      <rgbColor rgb="FFFBE4D5"/>
+      <rgbColor rgb="FFE2EEDA"/>
+      <rgbColor rgb="FF4472C4"/>
+      <rgbColor rgb="FF99AAC9"/>
+      <rgbColor rgb="FFB4C6E7"/>
+      <rgbColor rgb="FFA3AAB6"/>
+      <rgbColor rgb="FFD1D4DA"/>
+      <rgbColor rgb="FFC6D4ED"/>
       <rgbColor rgb="00000000"/>
-      <rgbColor rgb="ff8eaadb"/>
+      <rgbColor rgb="FF8EAADB"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" refreshedDate="0" recordCount="48" createdVersion="7">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedDate="0" createdVersion="7" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B49" sheet="Gironi - Tabella 1"/>
   </cacheSource>
@@ -2603,7 +2781,7 @@
     </cacheField>
   </cacheFields>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
   </extLst>
@@ -2808,7 +2986,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabella pivot2" cacheId="0" dataPosition="0" autoFormatId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" missingCaption="" pivotTableStyle="PivotStyleCustom01" updatedVersion="7" useAutoFormatting="1" createdVersion="7" indent="0" showEmptyCol="1" showEmptyRow="1" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000000000000}" name="Tabella pivot2" cacheId="0" dataPosition="0" autoFormatId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" missingCaption="" pivotTableStyle="PivotStyleCustom01" updatedVersion="7" useAutoFormatting="1" createdVersion="7" indent="0" showEmptyRow="1" showEmptyCol="1" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A2:C63" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="2">
     <pivotField name="Group" axis="axisRow" compact="0" numFmtId="49" outline="0" showAll="0" sortType="ascending">
@@ -3087,11 +3265,16 @@
     <i/>
   </colItems>
   <pivotTableStyleInfo name="PivotStyleCustom01" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 2013 - Tema 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - Tema 2022">
       <a:dk1>
@@ -3293,7 +3476,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -3311,7 +3494,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3340,7 +3523,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3365,7 +3548,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3390,7 +3573,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3415,7 +3598,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3440,7 +3623,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3465,7 +3648,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3490,7 +3673,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3515,7 +3698,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3540,7 +3723,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3553,9 +3736,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -3572,7 +3761,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -3590,7 +3779,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3615,7 +3804,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3640,7 +3829,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3665,7 +3854,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3690,7 +3879,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3715,7 +3904,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3740,7 +3929,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3765,7 +3954,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3790,7 +3979,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3815,7 +4004,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3828,9 +4017,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -3844,7 +4039,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -3862,7 +4057,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3891,7 +4086,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3916,7 +4111,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3941,7 +4136,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3966,7 +4161,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3991,7 +4186,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4016,7 +4211,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4041,7 +4236,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4066,7 +4261,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4091,7 +4286,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4104,96 +4299,104 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:D15"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.5547" customWidth="1"/>
+    <col min="2" max="4" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="50" customHeight="1">
-      <c r="B3" t="s" s="1">
+    <row r="3" spans="2:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C3"/>
-      <c r="D3"/>
-    </row>
-    <row r="7">
-      <c r="B7" t="s" s="2">
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+    </row>
+    <row r="7" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="s" s="3">
+    <row r="9" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="4"/>
-      <c r="C10" t="s" s="4">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s" s="5">
+      <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="s" s="3">
+    <row r="11" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="4"/>
-      <c r="C12" t="s" s="4">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s" s="5">
+      <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="s" s="3">
+    <row r="13" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="4"/>
-      <c r="C14" t="s" s="4">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D14" t="s" s="5">
+      <c r="D14" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="4"/>
-      <c r="C15" t="s" s="4">
+    <row r="15" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" t="s" s="5">
+      <c r="D15" s="4" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4202,266 +4405,294 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" location="'REGOLAMENTO'!R1C1" tooltip="" display="REGOLAMENTO"/>
-    <hyperlink ref="D12" location="'TABELLONE'!R1C1" tooltip="" display="TABELLONE"/>
-    <hyperlink ref="D14" location="'Gironi - Tabella pivot2'!R2C1" tooltip="" display="Gironi - Tabella pivot2"/>
-    <hyperlink ref="D15" location="'Gironi - Tabella 1'!R1C1" tooltip="" display="Gironi - Tabella 1"/>
+    <hyperlink ref="D10" location="'REGOLAMENTO'!R1C1" display="REGOLAMENTO" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D12" location="'TABELLONE'!R1C1" display="TABELLONE" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D14" location="'Gironi - Tabella pivot2'!R2C1" display="Gironi - Tabella pivot2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D15" location="'Gironi - Tabella 1'!R1C1" display="Gironi - Tabella 1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.35156" style="6" customWidth="1"/>
-    <col min="2" max="6" width="8.67188" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.85156" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9.36328125" style="5" customWidth="1"/>
+    <col min="2" max="6" width="8.6328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.05" customHeight="1">
-      <c r="A1" t="s" s="7">
+    <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" t="s" s="10">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" t="s" s="12">
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" t="s" s="14">
+      <c r="F2" s="71"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" t="s" s="16">
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="17"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" t="s" s="14">
+      <c r="F3" s="62"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" t="s" s="16">
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" t="s" s="14">
+      <c r="F4" s="62"/>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" t="s" s="16">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-    </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" t="s" s="14">
+      <c r="F5" s="62"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="74"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" t="s" s="16">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="17"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" t="s" s="14">
+      <c r="F7" s="62"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" t="s" s="16">
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="17"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" t="s" s="14">
+      <c r="F8" s="62"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" t="s" s="16">
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="17"/>
-    </row>
-    <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
-    </row>
-    <row r="11" ht="13.55" customHeight="1">
-      <c r="A11" t="s" s="14">
+      <c r="F9" s="62"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="72"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="74"/>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" t="s" s="16">
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="17"/>
-    </row>
-    <row r="12" ht="13.55" customHeight="1">
-      <c r="A12" t="s" s="14">
+      <c r="F11" s="62"/>
+    </row>
+    <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" t="s" s="16">
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="17"/>
-    </row>
-    <row r="13" ht="13.55" customHeight="1">
-      <c r="A13" t="s" s="14">
+      <c r="F12" s="62"/>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" t="s" s="16">
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" ht="13.55" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
-    </row>
-    <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" t="s" s="14">
+      <c r="F13" s="62"/>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" t="s" s="16">
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="17"/>
-    </row>
-    <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" t="s" s="14">
+      <c r="F15" s="62"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" t="s" s="16">
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="17"/>
-    </row>
-    <row r="17" ht="13.55" customHeight="1">
-      <c r="A17" t="s" s="14">
+      <c r="F16" s="62"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" t="s" s="16">
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="17"/>
-    </row>
-    <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" t="s" s="14">
+      <c r="F17" s="62"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" t="s" s="16">
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="17"/>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" t="s" s="14">
+      <c r="F18" s="62"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" t="s" s="16">
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="17"/>
-    </row>
-    <row r="20" ht="8.5" customHeight="1">
-      <c r="A20" t="s" s="21">
+      <c r="F19" s="62"/>
+    </row>
+    <row r="20" spans="1:6" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="23"/>
-    </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" ht="14.5" customHeight="1">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
+    </row>
+    <row r="21" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="78"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="80"/>
+    </row>
+    <row r="22" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="81"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
@@ -4471,35 +4702,9 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A20:F22"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -4507,2923 +4712,2854 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T82"/>
-  <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="14.5" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="9.17188" style="30" customWidth="1"/>
-    <col min="6" max="6" width="7.17188" style="30" customWidth="1"/>
-    <col min="7" max="7" width="13.3516" style="30" customWidth="1"/>
-    <col min="8" max="8" width="14.8516" style="30" customWidth="1"/>
-    <col min="9" max="9" width="5.17188" style="30" customWidth="1"/>
-    <col min="10" max="16" width="9.17188" style="30" customWidth="1"/>
-    <col min="17" max="17" width="13.5" style="30" customWidth="1"/>
-    <col min="18" max="20" width="9.17188" style="30" customWidth="1"/>
-    <col min="21" max="16384" width="9.17188" style="30" customWidth="1"/>
+    <col min="1" max="5" width="9.1796875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="5.1796875" style="5" customWidth="1"/>
+    <col min="10" max="16" width="9.1796875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.453125" style="5" customWidth="1"/>
+    <col min="18" max="21" width="9.1796875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="31"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="34"/>
-    </row>
-    <row r="2" ht="14.5" customHeight="1">
-      <c r="A2" t="s" s="35">
+    <row r="1" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="9"/>
+    </row>
+    <row r="2" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" t="s" s="37">
+      <c r="B2" s="126"/>
+      <c r="C2" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="41"/>
-    </row>
-    <row r="3" ht="14.5" customHeight="1">
-      <c r="A3" t="s" s="35">
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="12"/>
+    </row>
+    <row r="3" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" t="s" s="37">
+      <c r="B3" s="126"/>
+      <c r="C3" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="41"/>
-    </row>
-    <row r="4" ht="14.5" customHeight="1">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="41"/>
-    </row>
-    <row r="5" ht="14.5" customHeight="1">
-      <c r="A5" t="s" s="44">
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="12"/>
+    </row>
+    <row r="5" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="47"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="46"/>
-    </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" t="s" s="49">
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="86"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="87"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="88"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="88"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="86"/>
+    </row>
+    <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="52"/>
-      <c r="J7" t="s" s="49">
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="46"/>
-    </row>
-    <row r="8" ht="18.5" customHeight="1">
-      <c r="A8" t="s" s="54">
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="16"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s" s="55">
+      <c r="B8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s" s="55">
+      <c r="C8" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" t="s" s="55">
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="G8" t="s" s="55">
+      <c r="G8" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H8" t="s" s="57">
+      <c r="H8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="58"/>
-      <c r="J8" t="s" s="54">
+      <c r="I8" s="22"/>
+      <c r="J8" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="41"/>
-    </row>
-    <row r="9" ht="18.5" customHeight="1">
-      <c r="A9" s="61">
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="12"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="24">
         <v>46184</v>
       </c>
-      <c r="B9" t="s" s="62">
+      <c r="B9" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C9" t="s" s="63">
+      <c r="C9" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="65"/>
-      <c r="F9" t="s" s="62">
+      <c r="D9" s="102"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G9" t="s" s="62">
+      <c r="G9" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="H9" t="s" s="66">
+      <c r="H9" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="58"/>
-      <c r="J9" t="s" s="54">
+      <c r="I9" s="22"/>
+      <c r="J9" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="56"/>
-      <c r="L9" t="s" s="55">
+      <c r="K9" s="90"/>
+      <c r="L9" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" t="s" s="55">
+      <c r="M9" s="90"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="41"/>
-    </row>
-    <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="67">
+      <c r="P9" s="90"/>
+      <c r="Q9" s="92"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="12"/>
+    </row>
+    <row r="10" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="27">
         <v>46185</v>
       </c>
-      <c r="B10" t="s" s="68">
+      <c r="B10" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s" s="69">
+      <c r="C10" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="72">
+      <c r="D10" s="105"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="134">
         <v>1</v>
       </c>
-      <c r="G10" t="s" s="68">
+      <c r="G10" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="H10" t="s" s="73">
+      <c r="H10" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="58"/>
-      <c r="J10" t="s" s="74">
+      <c r="I10" s="22"/>
+      <c r="J10" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="75"/>
-      <c r="L10" t="s" s="76">
+      <c r="K10" s="97"/>
+      <c r="L10" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="77"/>
-      <c r="N10" s="77"/>
-      <c r="O10" t="s" s="76">
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="41"/>
-    </row>
-    <row r="11" ht="14.5" customHeight="1">
-      <c r="A11" s="67">
+      <c r="P10" s="99"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="12"/>
+    </row>
+    <row r="11" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="27">
         <v>46185</v>
       </c>
-      <c r="B11" t="s" s="68">
+      <c r="B11" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C11" t="s" s="69">
+      <c r="C11" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="72">
+      <c r="D11" s="105"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="134">
         <v>2</v>
       </c>
-      <c r="G11" s="79">
+      <c r="G11" s="136">
         <v>46054</v>
       </c>
-      <c r="H11" t="s" s="73">
+      <c r="H11" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="58"/>
-      <c r="J11" t="s" s="74">
+      <c r="I11" s="22"/>
+      <c r="J11" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="75"/>
-      <c r="L11" t="s" s="76">
+      <c r="K11" s="97"/>
+      <c r="L11" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="77"/>
-      <c r="N11" s="77"/>
-      <c r="O11" t="s" s="76">
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="78"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="41"/>
-    </row>
-    <row r="12" ht="14.5" customHeight="1">
-      <c r="A12" s="61">
+      <c r="P11" s="99"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="12"/>
+    </row>
+    <row r="12" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="24">
         <v>46186</v>
       </c>
-      <c r="B12" t="s" s="62">
+      <c r="B12" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C12" t="s" s="63">
+      <c r="C12" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="65"/>
-      <c r="F12" t="s" s="62">
+      <c r="D12" s="102"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="80">
+      <c r="G12" s="137">
         <v>46023</v>
       </c>
-      <c r="H12" t="s" s="66">
+      <c r="H12" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="58"/>
-      <c r="J12" t="s" s="74">
+      <c r="I12" s="22"/>
+      <c r="J12" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="75"/>
-      <c r="L12" t="s" s="76">
+      <c r="K12" s="97"/>
+      <c r="L12" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" t="s" s="76">
+      <c r="M12" s="99"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="77"/>
-      <c r="Q12" s="78"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="41"/>
-    </row>
-    <row r="13" ht="14.5" customHeight="1">
-      <c r="A13" s="61">
+      <c r="P12" s="99"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="24">
         <v>46186</v>
       </c>
-      <c r="B13" t="s" s="62">
+      <c r="B13" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C13" t="s" s="63">
+      <c r="C13" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="81">
+      <c r="D13" s="102"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="138">
         <v>2</v>
       </c>
-      <c r="G13" t="s" s="62">
+      <c r="G13" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="H13" t="s" s="66">
+      <c r="H13" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="58"/>
-      <c r="J13" t="s" s="74">
+      <c r="I13" s="22"/>
+      <c r="J13" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="75"/>
-      <c r="L13" t="s" s="76">
+      <c r="K13" s="97"/>
+      <c r="L13" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="77"/>
-      <c r="N13" s="77"/>
-      <c r="O13" t="s" s="76">
+      <c r="M13" s="99"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="P13" s="77"/>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="41"/>
-    </row>
-    <row r="14" ht="14.5" customHeight="1">
-      <c r="A14" s="67">
+      <c r="P13" s="99"/>
+      <c r="Q13" s="100"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="12"/>
+    </row>
+    <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="27">
         <v>46187</v>
       </c>
-      <c r="B14" t="s" s="68">
+      <c r="B14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s" s="69">
+      <c r="C14" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72">
+      <c r="D14" s="105"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="134">
         <v>1</v>
       </c>
-      <c r="G14" s="79">
+      <c r="G14" s="136">
         <v>46025</v>
       </c>
-      <c r="H14" t="s" s="73">
+      <c r="H14" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="58"/>
-      <c r="J14" t="s" s="74">
+      <c r="I14" s="22"/>
+      <c r="J14" s="96" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="75"/>
-      <c r="L14" t="s" s="76">
+      <c r="K14" s="97"/>
+      <c r="L14" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="M14" s="77"/>
-      <c r="N14" s="77"/>
-      <c r="O14" t="s" s="76">
+      <c r="M14" s="99"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="P14" s="77"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="41"/>
-    </row>
-    <row r="15" ht="14.5" customHeight="1">
-      <c r="A15" s="67">
+      <c r="P14" s="99"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="12"/>
+    </row>
+    <row r="15" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="27">
         <v>46187</v>
       </c>
-      <c r="B15" t="s" s="68">
+      <c r="B15" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="69">
+      <c r="C15" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="72">
+      <c r="D15" s="105"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="134">
         <v>2</v>
       </c>
-      <c r="G15" t="s" s="68">
+      <c r="G15" s="135" t="s">
         <v>81</v>
       </c>
-      <c r="H15" t="s" s="73">
+      <c r="H15" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="58"/>
-      <c r="J15" t="s" s="74">
+      <c r="I15" s="22"/>
+      <c r="J15" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="75"/>
-      <c r="L15" t="s" s="76">
+      <c r="K15" s="97"/>
+      <c r="L15" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="M15" s="77"/>
-      <c r="N15" s="77"/>
-      <c r="O15" t="s" s="76">
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="41"/>
-    </row>
-    <row r="16" ht="14.5" customHeight="1">
-      <c r="A16" s="67">
+      <c r="P15" s="99"/>
+      <c r="Q15" s="100"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="12"/>
+    </row>
+    <row r="16" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="27">
         <v>46187</v>
       </c>
-      <c r="B16" t="s" s="68">
+      <c r="B16" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s" s="69">
+      <c r="C16" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="72">
+      <c r="D16" s="105"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="134">
         <v>2</v>
       </c>
-      <c r="G16" s="79">
+      <c r="G16" s="136">
         <v>46023</v>
       </c>
-      <c r="H16" t="s" s="73">
+      <c r="H16" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="I16" s="58"/>
-      <c r="J16" t="s" s="74">
+      <c r="I16" s="22"/>
+      <c r="J16" s="96" t="s">
         <v>88</v>
       </c>
-      <c r="K16" s="75"/>
-      <c r="L16" t="s" s="76">
+      <c r="K16" s="97"/>
+      <c r="L16" s="98" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="77"/>
-      <c r="N16" s="77"/>
-      <c r="O16" t="s" s="76">
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="41"/>
-    </row>
-    <row r="17" ht="14.5" customHeight="1">
-      <c r="A17" s="67">
+      <c r="P16" s="99"/>
+      <c r="Q16" s="100"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="12"/>
+    </row>
+    <row r="17" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="27">
         <v>46187</v>
       </c>
-      <c r="B17" t="s" s="68">
+      <c r="B17" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="s" s="69">
+      <c r="C17" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="72">
+      <c r="D17" s="105"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="134">
         <v>1</v>
       </c>
-      <c r="G17" t="s" s="68">
+      <c r="G17" s="135" t="s">
         <v>92</v>
       </c>
-      <c r="H17" t="s" s="73">
+      <c r="H17" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="58"/>
-      <c r="J17" t="s" s="74">
+      <c r="I17" s="22"/>
+      <c r="J17" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="K17" s="75"/>
-      <c r="L17" t="s" s="76">
+      <c r="K17" s="97"/>
+      <c r="L17" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" t="s" s="76">
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="41"/>
-    </row>
-    <row r="18" ht="14.5" customHeight="1">
-      <c r="A18" s="67">
+      <c r="P17" s="99"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="12"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="27">
         <v>46187</v>
       </c>
-      <c r="B18" t="s" s="68">
+      <c r="B18" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C18" t="s" s="69">
+      <c r="C18" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="71"/>
-      <c r="F18" t="s" s="68">
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="79">
+      <c r="G18" s="136">
         <v>46024</v>
       </c>
-      <c r="H18" t="s" s="73">
+      <c r="H18" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="58"/>
-      <c r="J18" t="s" s="74">
+      <c r="I18" s="22"/>
+      <c r="J18" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="K18" s="75"/>
-      <c r="L18" t="s" s="76">
+      <c r="K18" s="97"/>
+      <c r="L18" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="M18" s="77"/>
-      <c r="N18" s="77"/>
-      <c r="O18" t="s" s="76">
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="40"/>
-      <c r="T18" s="41"/>
-    </row>
-    <row r="19" ht="14.5" customHeight="1">
-      <c r="A19" s="61">
+      <c r="P18" s="99"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="12"/>
+    </row>
+    <row r="19" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="24">
         <v>46188</v>
       </c>
-      <c r="B19" t="s" s="62">
+      <c r="B19" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C19" t="s" s="63">
+      <c r="C19" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="65"/>
-      <c r="F19" t="s" s="62">
+      <c r="D19" s="102"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="80">
+      <c r="G19" s="137">
         <v>46023</v>
       </c>
-      <c r="H19" t="s" s="66">
+      <c r="H19" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="58"/>
-      <c r="J19" t="s" s="74">
+      <c r="I19" s="22"/>
+      <c r="J19" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="K19" s="75"/>
-      <c r="L19" t="s" s="76">
+      <c r="K19" s="97"/>
+      <c r="L19" s="98" t="s">
         <v>105</v>
       </c>
-      <c r="M19" s="77"/>
-      <c r="N19" s="77"/>
-      <c r="O19" t="s" s="76">
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="60"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="41"/>
-    </row>
-    <row r="20" ht="14.5" customHeight="1">
-      <c r="A20" s="61">
+      <c r="P19" s="99"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="12"/>
+    </row>
+    <row r="20" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="24">
         <v>46188</v>
       </c>
-      <c r="B20" t="s" s="62">
+      <c r="B20" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C20" t="s" s="63">
+      <c r="C20" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="81">
+      <c r="D20" s="102"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="138">
         <v>1</v>
       </c>
-      <c r="G20" t="s" s="62">
+      <c r="G20" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H20" t="s" s="66">
+      <c r="H20" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="58"/>
-      <c r="J20" t="s" s="74">
+      <c r="I20" s="22"/>
+      <c r="J20" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="75"/>
-      <c r="L20" t="s" s="76">
+      <c r="K20" s="97"/>
+      <c r="L20" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="M20" s="77"/>
-      <c r="N20" s="77"/>
-      <c r="O20" t="s" s="76">
+      <c r="M20" s="99"/>
+      <c r="N20" s="99"/>
+      <c r="O20" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="P20" s="77"/>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="60"/>
-      <c r="S20" s="40"/>
-      <c r="T20" s="41"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="61">
+      <c r="P20" s="99"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="12"/>
+    </row>
+    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="24">
         <v>46188</v>
       </c>
-      <c r="B21" t="s" s="62">
+      <c r="B21" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C21" t="s" s="63">
+      <c r="C21" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="81">
+      <c r="D21" s="102"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="138">
         <v>1</v>
       </c>
-      <c r="G21" t="s" s="62">
+      <c r="G21" s="133" t="s">
         <v>113</v>
       </c>
-      <c r="H21" t="s" s="66">
+      <c r="H21" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="I21" s="58"/>
-      <c r="J21" t="s" s="82">
+      <c r="I21" s="22"/>
+      <c r="J21" s="110" t="s">
         <v>115</v>
       </c>
-      <c r="K21" s="83"/>
-      <c r="L21" t="s" s="84">
+      <c r="K21" s="111"/>
+      <c r="L21" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="85"/>
-      <c r="N21" s="85"/>
-      <c r="O21" t="s" s="84">
+      <c r="M21" s="108"/>
+      <c r="N21" s="108"/>
+      <c r="O21" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="86"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="41"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="61">
+      <c r="P21" s="108"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="12"/>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="24">
         <v>46188</v>
       </c>
-      <c r="B22" t="s" s="62">
+      <c r="B22" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C22" t="s" s="63">
+      <c r="C22" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="81">
+      <c r="D22" s="102"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="138">
         <v>1</v>
       </c>
-      <c r="G22" s="80">
+      <c r="G22" s="137">
         <v>46025</v>
       </c>
-      <c r="H22" t="s" s="66">
+      <c r="H22" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="41"/>
-    </row>
-    <row r="23" ht="18.5" customHeight="1">
-      <c r="A23" s="67">
+      <c r="I22" s="23"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="12"/>
+    </row>
+    <row r="23" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="27">
         <v>46189</v>
       </c>
-      <c r="B23" t="s" s="68">
+      <c r="B23" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C23" t="s" s="69">
+      <c r="C23" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="70"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="72">
+      <c r="D23" s="105"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="134">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="68">
+      <c r="G23" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="H23" t="s" s="73">
+      <c r="H23" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="I23" s="60"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="89"/>
-      <c r="L23" t="s" s="90">
+      <c r="I23" s="23"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="92"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="41"/>
-    </row>
-    <row r="24" ht="14.5" customHeight="1">
-      <c r="A24" s="67">
+      <c r="M23" s="113"/>
+      <c r="N23" s="113"/>
+      <c r="O23" s="113"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="12"/>
+    </row>
+    <row r="24" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="27">
         <v>46189</v>
       </c>
-      <c r="B24" t="s" s="68">
+      <c r="B24" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C24" t="s" s="69">
+      <c r="C24" s="104" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="72">
+      <c r="D24" s="105"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="134">
         <v>1</v>
       </c>
-      <c r="G24" t="s" s="68">
+      <c r="G24" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="H24" t="s" s="73">
+      <c r="H24" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="89"/>
-      <c r="L24" t="s" s="93">
+      <c r="I24" s="23"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="M24" s="77"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="77"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="41"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="67">
+      <c r="M24" s="99"/>
+      <c r="N24" s="99"/>
+      <c r="O24" s="99"/>
+      <c r="P24" s="100"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="12"/>
+    </row>
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="27">
         <v>46189</v>
       </c>
-      <c r="B25" t="s" s="68">
+      <c r="B25" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C25" t="s" s="69">
+      <c r="C25" s="104" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="72">
+      <c r="D25" s="105"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="134">
         <v>1</v>
       </c>
-      <c r="G25" s="79">
+      <c r="G25" s="136">
         <v>46025</v>
       </c>
-      <c r="H25" t="s" s="73">
+      <c r="H25" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="I25" s="60"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="41"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="61">
+      <c r="I25" s="23"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="108"/>
+      <c r="O25" s="108"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="12"/>
+    </row>
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="24">
         <v>46190</v>
       </c>
-      <c r="B26" t="s" s="62">
+      <c r="B26" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C26" t="s" s="63">
+      <c r="C26" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="81">
+      <c r="D26" s="102"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="138">
         <v>2</v>
       </c>
-      <c r="G26" t="s" s="62">
+      <c r="G26" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="H26" t="s" s="66">
+      <c r="H26" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="I26" s="60"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="88"/>
-      <c r="O26" s="88"/>
-      <c r="P26" s="88"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="41"/>
-    </row>
-    <row r="27" ht="18.5" customHeight="1">
-      <c r="A27" s="61">
+      <c r="I26" s="23"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="12"/>
+    </row>
+    <row r="27" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="24">
         <v>46190</v>
       </c>
-      <c r="B27" t="s" s="62">
+      <c r="B27" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C27" t="s" s="63">
+      <c r="C27" s="101" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="81">
+      <c r="D27" s="102"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="138">
         <v>1</v>
       </c>
-      <c r="G27" t="s" s="62">
+      <c r="G27" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="H27" t="s" s="66">
+      <c r="H27" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="60"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="89"/>
-      <c r="L27" t="s" s="90">
+      <c r="I27" s="23"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="112" t="s">
         <v>132</v>
       </c>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="92"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="41"/>
-    </row>
-    <row r="28" ht="14.5" customHeight="1">
-      <c r="A28" s="61">
+      <c r="M27" s="113"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="12"/>
+    </row>
+    <row r="28" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="24">
         <v>46190</v>
       </c>
-      <c r="B28" t="s" s="62">
+      <c r="B28" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C28" t="s" s="63">
+      <c r="C28" s="101" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="81">
+      <c r="D28" s="102"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="138">
         <v>1</v>
       </c>
-      <c r="G28" t="s" s="62">
+      <c r="G28" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H28" t="s" s="66">
+      <c r="H28" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="I28" s="60"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="89"/>
-      <c r="L28" t="s" s="74">
+      <c r="I28" s="23"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="M28" t="s" s="76">
+      <c r="M28" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="N28" s="77"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="40"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="41"/>
-    </row>
-    <row r="29" ht="14.5" customHeight="1">
-      <c r="A29" s="61">
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="100"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="12"/>
+    </row>
+    <row r="29" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="24">
         <v>46190</v>
       </c>
-      <c r="B29" t="s" s="62">
+      <c r="B29" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C29" t="s" s="63">
+      <c r="C29" s="101" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="64"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="81">
+      <c r="D29" s="102"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="138">
         <v>1</v>
       </c>
-      <c r="G29" t="s" s="62">
+      <c r="G29" s="133" t="s">
         <v>113</v>
       </c>
-      <c r="H29" t="s" s="66">
+      <c r="H29" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="I29" s="60"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="77"/>
-      <c r="P29" s="78"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="41"/>
-    </row>
-    <row r="30" ht="14.5" customHeight="1">
-      <c r="A30" s="61">
+      <c r="I29" s="23"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="117"/>
+      <c r="M29" s="99"/>
+      <c r="N29" s="99"/>
+      <c r="O29" s="99"/>
+      <c r="P29" s="100"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="12"/>
+    </row>
+    <row r="30" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="24">
         <v>46190</v>
       </c>
-      <c r="B30" t="s" s="62">
+      <c r="B30" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C30" t="s" s="63">
+      <c r="C30" s="101" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65"/>
-      <c r="F30" t="s" s="62">
+      <c r="D30" s="102"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="80">
+      <c r="G30" s="137">
         <v>46055</v>
       </c>
-      <c r="H30" t="s" s="66">
+      <c r="H30" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="I30" s="60"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="89"/>
-      <c r="L30" t="s" s="74">
+      <c r="I30" s="23"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="M30" t="s" s="76">
+      <c r="M30" s="98" t="s">
         <v>142</v>
       </c>
-      <c r="N30" s="77"/>
-      <c r="O30" s="77"/>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="41"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="67">
+      <c r="N30" s="99"/>
+      <c r="O30" s="99"/>
+      <c r="P30" s="100"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="12"/>
+    </row>
+    <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="27">
         <v>46191</v>
       </c>
-      <c r="B31" t="s" s="68">
+      <c r="B31" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C31" t="s" s="69">
+      <c r="C31" s="104" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="70"/>
-      <c r="E31" s="71"/>
-      <c r="F31" t="s" s="68">
+      <c r="D31" s="105"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G31" t="s" s="68">
+      <c r="G31" s="135" t="s">
         <v>144</v>
       </c>
-      <c r="H31" t="s" s="73">
+      <c r="H31" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="I31" s="60"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="40"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="41"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="67">
+      <c r="I31" s="23"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="118"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="108"/>
+      <c r="O31" s="108"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="12"/>
+    </row>
+    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="27">
         <v>46191</v>
       </c>
-      <c r="B32" t="s" s="68">
+      <c r="B32" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C32" t="s" s="69">
+      <c r="C32" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="70"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72">
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="134">
         <v>2</v>
       </c>
-      <c r="G32" s="79">
+      <c r="G32" s="136">
         <v>46054</v>
       </c>
-      <c r="H32" t="s" s="73">
+      <c r="H32" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="60"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="88"/>
-      <c r="O32" s="88"/>
-      <c r="P32" s="88"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="40"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="41"/>
-    </row>
-    <row r="33" ht="18.5" customHeight="1">
-      <c r="A33" s="97"/>
-      <c r="B33" s="98"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="98"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="89"/>
-      <c r="L33" t="s" s="90">
+      <c r="I32" s="23"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="12"/>
+    </row>
+    <row r="33" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="119"/>
+      <c r="B33" s="120"/>
+      <c r="C33" s="120"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="121"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="112" t="s">
         <v>148</v>
       </c>
-      <c r="M33" s="91"/>
-      <c r="N33" s="91"/>
-      <c r="O33" s="91"/>
-      <c r="P33" s="92"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="40"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="41"/>
-    </row>
-    <row r="34" ht="14.5" customHeight="1">
-      <c r="A34" s="67">
+      <c r="M33" s="113"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="113"/>
+      <c r="P33" s="114"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="12"/>
+    </row>
+    <row r="34" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="27">
         <v>46191</v>
       </c>
-      <c r="B34" t="s" s="68">
+      <c r="B34" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C34" t="s" s="69">
+      <c r="C34" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="70"/>
-      <c r="E34" s="71"/>
-      <c r="F34" t="s" s="68">
+      <c r="D34" s="105"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="79">
+      <c r="G34" s="136">
         <v>46023</v>
       </c>
-      <c r="H34" t="s" s="73">
+      <c r="H34" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="I34" s="60"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="89"/>
-      <c r="L34" t="s" s="93">
+      <c r="I34" s="23"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="115" t="s">
         <v>140</v>
       </c>
-      <c r="M34" s="77"/>
-      <c r="N34" s="77"/>
-      <c r="O34" s="77"/>
-      <c r="P34" s="78"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="40"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="41"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="67">
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="100"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="12"/>
+    </row>
+    <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="27">
         <v>46191</v>
       </c>
-      <c r="B35" t="s" s="68">
+      <c r="B35" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C35" t="s" s="69">
+      <c r="C35" s="104" t="s">
         <v>151</v>
       </c>
-      <c r="D35" s="70"/>
-      <c r="E35" s="71"/>
-      <c r="F35" t="s" s="68">
+      <c r="D35" s="105"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G35" s="79">
+      <c r="G35" s="136">
         <v>46054</v>
       </c>
-      <c r="H35" t="s" s="73">
+      <c r="H35" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="I35" s="60"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="85"/>
-      <c r="N35" s="85"/>
-      <c r="O35" s="85"/>
-      <c r="P35" s="86"/>
-      <c r="Q35" s="60"/>
-      <c r="R35" s="40"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="41"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="61">
+      <c r="I35" s="23"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="116"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="109"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="12"/>
+    </row>
+    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="24">
         <v>46192</v>
       </c>
-      <c r="B36" t="s" s="62">
+      <c r="B36" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C36" t="s" s="63">
+      <c r="C36" s="101" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="81">
+      <c r="D36" s="102"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="138">
         <v>1</v>
       </c>
-      <c r="G36" t="s" s="62">
+      <c r="G36" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H36" t="s" s="66">
+      <c r="H36" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="I36" s="60"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="88"/>
-      <c r="N36" s="88"/>
-      <c r="O36" s="88"/>
-      <c r="P36" s="88"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="41"/>
-    </row>
-    <row r="37" ht="18.5" customHeight="1">
-      <c r="A37" s="61">
+      <c r="I36" s="23"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="12"/>
+    </row>
+    <row r="37" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="24">
         <v>46192</v>
       </c>
-      <c r="B37" t="s" s="62">
+      <c r="B37" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C37" t="s" s="63">
+      <c r="C37" s="101" t="s">
         <v>155</v>
       </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="65"/>
-      <c r="F37" t="s" s="62">
+      <c r="D37" s="102"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G37" t="s" s="62">
+      <c r="G37" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="H37" t="s" s="66">
+      <c r="H37" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="I37" s="60"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="89"/>
-      <c r="L37" t="s" s="90">
+      <c r="I37" s="23"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="112" t="s">
         <v>157</v>
       </c>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="92"/>
-      <c r="Q37" s="60"/>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="41"/>
-    </row>
-    <row r="38" ht="14.5" customHeight="1">
-      <c r="A38" s="61">
+      <c r="M37" s="113"/>
+      <c r="N37" s="113"/>
+      <c r="O37" s="113"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="12"/>
+    </row>
+    <row r="38" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="24">
         <v>46192</v>
       </c>
-      <c r="B38" t="s" s="62">
+      <c r="B38" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C38" t="s" s="63">
+      <c r="C38" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="81">
+      <c r="D38" s="102"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="138">
         <v>1</v>
       </c>
-      <c r="G38" s="80">
+      <c r="G38" s="137">
         <v>46023</v>
       </c>
-      <c r="H38" t="s" s="66">
+      <c r="H38" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="I38" s="60"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="89"/>
-      <c r="L38" t="s" s="93">
+      <c r="I38" s="23"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="115" t="s">
         <v>138</v>
       </c>
-      <c r="M38" s="77"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="77"/>
-      <c r="P38" s="78"/>
-      <c r="Q38" s="60"/>
-      <c r="R38" s="40"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="41"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="67">
+      <c r="M38" s="99"/>
+      <c r="N38" s="99"/>
+      <c r="O38" s="99"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="12"/>
+    </row>
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="27">
         <v>46193</v>
       </c>
-      <c r="B39" t="s" s="68">
+      <c r="B39" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C39" t="s" s="69">
+      <c r="C39" s="104" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="70"/>
-      <c r="E39" s="71"/>
-      <c r="F39" t="s" s="68">
+      <c r="D39" s="105"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="79">
+      <c r="G39" s="136">
         <v>46055</v>
       </c>
-      <c r="H39" t="s" s="73">
+      <c r="H39" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="I39" s="60"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="94"/>
-      <c r="M39" s="85"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="85"/>
-      <c r="P39" s="86"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="40"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="41"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="67">
+      <c r="I39" s="23"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="116"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="108"/>
+      <c r="O39" s="108"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="12"/>
+    </row>
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="27">
         <v>46193</v>
       </c>
-      <c r="B40" t="s" s="68">
+      <c r="B40" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C40" t="s" s="69">
+      <c r="C40" s="104" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="70"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="72">
+      <c r="D40" s="105"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="134">
         <v>1</v>
       </c>
-      <c r="G40" t="s" s="68">
+      <c r="G40" s="135" t="s">
         <v>92</v>
       </c>
-      <c r="H40" t="s" s="73">
+      <c r="H40" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="I40" s="60"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="88"/>
-      <c r="M40" s="88"/>
-      <c r="N40" s="88"/>
-      <c r="O40" s="88"/>
-      <c r="P40" s="88"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="40"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="41"/>
-    </row>
-    <row r="41" ht="18.5" customHeight="1">
-      <c r="A41" s="67">
+      <c r="I40" s="23"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="12"/>
+    </row>
+    <row r="41" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="27">
         <v>46193</v>
       </c>
-      <c r="B41" t="s" s="68">
+      <c r="B41" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C41" t="s" s="69">
+      <c r="C41" s="104" t="s">
         <v>164</v>
       </c>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="72">
+      <c r="D41" s="105"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="134">
         <v>1</v>
       </c>
-      <c r="G41" s="79">
+      <c r="G41" s="136">
         <v>46024</v>
       </c>
-      <c r="H41" t="s" s="73">
+      <c r="H41" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="I41" s="60"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="89"/>
-      <c r="L41" t="s" s="90">
+      <c r="I41" s="23"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="112" t="s">
         <v>166</v>
       </c>
-      <c r="M41" s="91"/>
-      <c r="N41" s="91"/>
-      <c r="O41" s="91"/>
-      <c r="P41" s="92"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="40"/>
-      <c r="S41" s="40"/>
-      <c r="T41" s="41"/>
-    </row>
-    <row r="42" ht="14.5" customHeight="1">
-      <c r="A42" s="67">
+      <c r="M41" s="113"/>
+      <c r="N41" s="113"/>
+      <c r="O41" s="113"/>
+      <c r="P41" s="114"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="12"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="27">
         <v>46193</v>
       </c>
-      <c r="B42" t="s" s="68">
+      <c r="B42" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C42" t="s" s="69">
+      <c r="C42" s="104" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="70"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="72">
+      <c r="D42" s="105"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="134">
         <v>1</v>
       </c>
-      <c r="G42" s="79">
+      <c r="G42" s="136">
         <v>46025</v>
       </c>
-      <c r="H42" t="s" s="73">
+      <c r="H42" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I42" s="60"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="89"/>
-      <c r="L42" t="s" s="93">
+      <c r="I42" s="23"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="M42" s="77"/>
-      <c r="N42" s="77"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="40"/>
-      <c r="S42" s="40"/>
-      <c r="T42" s="41"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="67">
+      <c r="M42" s="99"/>
+      <c r="N42" s="99"/>
+      <c r="O42" s="99"/>
+      <c r="P42" s="100"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="12"/>
+    </row>
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="27">
         <v>46193</v>
       </c>
-      <c r="B43" t="s" s="68">
+      <c r="B43" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C43" t="s" s="69">
+      <c r="C43" s="104" t="s">
         <v>169</v>
       </c>
-      <c r="D43" s="70"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="72">
+      <c r="D43" s="105"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="134">
         <v>1</v>
       </c>
-      <c r="G43" s="79">
+      <c r="G43" s="136">
         <v>46024</v>
       </c>
-      <c r="H43" t="s" s="73">
+      <c r="H43" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="I43" s="60"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="94"/>
-      <c r="M43" s="85"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="85"/>
-      <c r="P43" s="86"/>
-      <c r="Q43" s="60"/>
-      <c r="R43" s="40"/>
-      <c r="S43" s="40"/>
-      <c r="T43" s="41"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="61">
+      <c r="I43" s="23"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="116"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
+      <c r="O43" s="108"/>
+      <c r="P43" s="109"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
+      <c r="T43" s="12"/>
+    </row>
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="24">
         <v>46194</v>
       </c>
-      <c r="B44" t="s" s="62">
+      <c r="B44" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C44" t="s" s="63">
+      <c r="C44" s="101" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="64"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="81">
+      <c r="D44" s="102"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="138">
         <v>1</v>
       </c>
-      <c r="G44" t="s" s="62">
+      <c r="G44" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="H44" t="s" s="66">
+      <c r="H44" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="I44" s="60"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="88"/>
-      <c r="M44" s="88"/>
-      <c r="N44" s="88"/>
-      <c r="O44" s="88"/>
-      <c r="P44" s="88"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="40"/>
-      <c r="S44" s="40"/>
-      <c r="T44" s="41"/>
-    </row>
-    <row r="45" ht="18.5" customHeight="1">
-      <c r="A45" s="61">
+      <c r="I44" s="23"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="12"/>
+    </row>
+    <row r="45" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="24">
         <v>46194</v>
       </c>
-      <c r="B45" t="s" s="62">
+      <c r="B45" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C45" t="s" s="63">
+      <c r="C45" s="101" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="64"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="81">
+      <c r="D45" s="102"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="138">
         <v>2</v>
       </c>
-      <c r="G45" t="s" s="62">
+      <c r="G45" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="H45" t="s" s="66">
+      <c r="H45" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="I45" s="60"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="89"/>
-      <c r="L45" t="s" s="90">
+      <c r="I45" s="23"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="M45" s="91"/>
-      <c r="N45" s="91"/>
-      <c r="O45" s="91"/>
-      <c r="P45" s="92"/>
-      <c r="Q45" s="60"/>
-      <c r="R45" s="40"/>
-      <c r="S45" s="40"/>
-      <c r="T45" s="41"/>
-    </row>
-    <row r="46" ht="14.5" customHeight="1">
-      <c r="A46" s="61">
+      <c r="M45" s="113"/>
+      <c r="N45" s="113"/>
+      <c r="O45" s="113"/>
+      <c r="P45" s="114"/>
+      <c r="Q45" s="23"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="12"/>
+    </row>
+    <row r="46" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="24">
         <v>46194</v>
       </c>
-      <c r="B46" t="s" s="62">
+      <c r="B46" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C46" t="s" s="63">
+      <c r="C46" s="101" t="s">
         <v>176</v>
       </c>
-      <c r="D46" s="64"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="81">
+      <c r="D46" s="102"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="138">
         <v>1</v>
       </c>
-      <c r="G46" t="s" s="62">
+      <c r="G46" s="133" t="s">
         <v>113</v>
       </c>
-      <c r="H46" t="s" s="66">
+      <c r="H46" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="I46" s="60"/>
-      <c r="J46" s="40"/>
-      <c r="K46" s="89"/>
-      <c r="L46" t="s" s="93">
+      <c r="I46" s="23"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="115" t="s">
         <v>177</v>
       </c>
-      <c r="M46" s="77"/>
-      <c r="N46" s="77"/>
-      <c r="O46" s="77"/>
-      <c r="P46" s="78"/>
-      <c r="Q46" s="60"/>
-      <c r="R46" s="40"/>
-      <c r="S46" s="40"/>
-      <c r="T46" s="41"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="61">
+      <c r="M46" s="99"/>
+      <c r="N46" s="99"/>
+      <c r="O46" s="99"/>
+      <c r="P46" s="100"/>
+      <c r="Q46" s="23"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="12"/>
+    </row>
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="24">
         <v>46194</v>
       </c>
-      <c r="B47" t="s" s="62">
+      <c r="B47" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C47" t="s" s="63">
+      <c r="C47" s="101" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="81">
+      <c r="D47" s="102"/>
+      <c r="E47" s="103"/>
+      <c r="F47" s="138">
         <v>1</v>
       </c>
-      <c r="G47" t="s" s="62">
+      <c r="G47" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H47" t="s" s="66">
+      <c r="H47" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="I47" s="60"/>
-      <c r="J47" s="40"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="94"/>
-      <c r="M47" s="85"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="85"/>
-      <c r="P47" s="86"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="40"/>
-      <c r="S47" s="40"/>
-      <c r="T47" s="41"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="67">
+      <c r="I47" s="23"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="116"/>
+      <c r="M47" s="108"/>
+      <c r="N47" s="108"/>
+      <c r="O47" s="108"/>
+      <c r="P47" s="109"/>
+      <c r="Q47" s="23"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+      <c r="T47" s="12"/>
+    </row>
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="27">
         <v>46195</v>
       </c>
-      <c r="B48" t="s" s="68">
+      <c r="B48" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C48" t="s" s="69">
+      <c r="C48" s="104" t="s">
         <v>180</v>
       </c>
-      <c r="D48" s="70"/>
-      <c r="E48" s="71"/>
-      <c r="F48" s="72">
+      <c r="D48" s="105"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="134">
         <v>1</v>
       </c>
-      <c r="G48" s="79">
+      <c r="G48" s="136">
         <v>46023</v>
       </c>
-      <c r="H48" t="s" s="73">
+      <c r="H48" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="I48" s="60"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="88"/>
-      <c r="M48" s="88"/>
-      <c r="N48" s="88"/>
-      <c r="O48" s="88"/>
-      <c r="P48" s="88"/>
-      <c r="Q48" s="40"/>
-      <c r="R48" s="40"/>
-      <c r="S48" s="40"/>
-      <c r="T48" s="41"/>
-    </row>
-    <row r="49" ht="18.5" customHeight="1">
-      <c r="A49" s="67">
+      <c r="I48" s="23"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+      <c r="T48" s="12"/>
+    </row>
+    <row r="49" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="27">
         <v>46195</v>
       </c>
-      <c r="B49" t="s" s="68">
+      <c r="B49" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C49" t="s" s="69">
+      <c r="C49" s="104" t="s">
         <v>182</v>
       </c>
-      <c r="D49" s="70"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="72">
+      <c r="D49" s="105"/>
+      <c r="E49" s="106"/>
+      <c r="F49" s="134">
         <v>2</v>
       </c>
-      <c r="G49" t="s" s="68">
+      <c r="G49" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="H49" t="s" s="73">
+      <c r="H49" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="I49" s="60"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="89"/>
-      <c r="L49" t="s" s="90">
+      <c r="I49" s="23"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="M49" s="91"/>
-      <c r="N49" s="91"/>
-      <c r="O49" s="91"/>
-      <c r="P49" s="92"/>
-      <c r="Q49" s="60"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="40"/>
-      <c r="T49" s="41"/>
-    </row>
-    <row r="50" ht="14.5" customHeight="1">
-      <c r="A50" s="67">
+      <c r="M49" s="113"/>
+      <c r="N49" s="113"/>
+      <c r="O49" s="113"/>
+      <c r="P49" s="114"/>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="12"/>
+    </row>
+    <row r="50" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="27">
         <v>46195</v>
       </c>
-      <c r="B50" t="s" s="68">
+      <c r="B50" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C50" t="s" s="69">
+      <c r="C50" s="104" t="s">
         <v>185</v>
       </c>
-      <c r="D50" s="70"/>
-      <c r="E50" s="71"/>
-      <c r="F50" s="72">
+      <c r="D50" s="105"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="134">
         <v>1</v>
       </c>
-      <c r="G50" s="79">
+      <c r="G50" s="136">
         <v>46024</v>
       </c>
-      <c r="H50" t="s" s="73">
+      <c r="H50" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="I50" s="60"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="89"/>
-      <c r="L50" t="s" s="93">
+      <c r="I50" s="23"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="M50" s="77"/>
-      <c r="N50" s="77"/>
-      <c r="O50" s="77"/>
-      <c r="P50" s="78"/>
-      <c r="Q50" s="60"/>
-      <c r="R50" s="40"/>
-      <c r="S50" s="40"/>
-      <c r="T50" s="41"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="67">
+      <c r="M50" s="99"/>
+      <c r="N50" s="99"/>
+      <c r="O50" s="99"/>
+      <c r="P50" s="100"/>
+      <c r="Q50" s="23"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+      <c r="T50" s="12"/>
+    </row>
+    <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="27">
         <v>46195</v>
       </c>
-      <c r="B51" t="s" s="68">
+      <c r="B51" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C51" t="s" s="69">
+      <c r="C51" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="D51" s="70"/>
-      <c r="E51" s="71"/>
-      <c r="F51" s="72">
+      <c r="D51" s="105"/>
+      <c r="E51" s="106"/>
+      <c r="F51" s="134">
         <v>1</v>
       </c>
-      <c r="G51" t="s" s="68">
+      <c r="G51" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="H51" t="s" s="73">
+      <c r="H51" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="I51" s="60"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="89"/>
-      <c r="L51" s="94"/>
-      <c r="M51" s="85"/>
-      <c r="N51" s="85"/>
-      <c r="O51" s="85"/>
-      <c r="P51" s="86"/>
-      <c r="Q51" s="60"/>
-      <c r="R51" s="40"/>
-      <c r="S51" s="40"/>
-      <c r="T51" s="41"/>
-    </row>
-    <row r="52" ht="14.5" customHeight="1">
-      <c r="A52" s="61">
+      <c r="I51" s="23"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="116"/>
+      <c r="M51" s="108"/>
+      <c r="N51" s="108"/>
+      <c r="O51" s="108"/>
+      <c r="P51" s="109"/>
+      <c r="Q51" s="23"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
+      <c r="T51" s="12"/>
+    </row>
+    <row r="52" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="24">
         <v>46196</v>
       </c>
-      <c r="B52" t="s" s="62">
+      <c r="B52" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C52" t="s" s="63">
+      <c r="C52" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
-      <c r="F52" t="s" s="62">
+      <c r="D52" s="102"/>
+      <c r="E52" s="103"/>
+      <c r="F52" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G52" s="80">
+      <c r="G52" s="137">
         <v>46025</v>
       </c>
-      <c r="H52" t="s" s="66">
+      <c r="H52" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="I52" s="60"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="40"/>
-      <c r="L52" s="87"/>
-      <c r="M52" s="87"/>
-      <c r="N52" s="87"/>
-      <c r="O52" s="87"/>
-      <c r="P52" s="87"/>
-      <c r="Q52" s="40"/>
-      <c r="R52" s="40"/>
-      <c r="S52" s="40"/>
-      <c r="T52" s="41"/>
-    </row>
-    <row r="53" ht="14.5" customHeight="1">
-      <c r="A53" s="61">
+      <c r="I52" s="23"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+      <c r="T52" s="12"/>
+    </row>
+    <row r="53" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="24">
         <v>46196</v>
       </c>
-      <c r="B53" t="s" s="62">
+      <c r="B53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C53" t="s" s="63">
+      <c r="C53" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="81">
+      <c r="D53" s="102"/>
+      <c r="E53" s="103"/>
+      <c r="F53" s="138">
         <v>2</v>
       </c>
-      <c r="G53" t="s" s="62">
+      <c r="G53" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="H53" t="s" s="66">
+      <c r="H53" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="I53" s="60"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="40"/>
-      <c r="Q53" s="40"/>
-      <c r="R53" s="40"/>
-      <c r="S53" s="40"/>
-      <c r="T53" s="41"/>
-    </row>
-    <row r="54" ht="14.5" customHeight="1">
-      <c r="A54" s="61">
+      <c r="I53" s="23"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+      <c r="T53" s="12"/>
+    </row>
+    <row r="54" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="24">
         <v>46196</v>
       </c>
-      <c r="B54" t="s" s="62">
+      <c r="B54" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C54" t="s" s="63">
+      <c r="C54" s="101" t="s">
         <v>193</v>
       </c>
-      <c r="D54" s="64"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="81">
+      <c r="D54" s="102"/>
+      <c r="E54" s="103"/>
+      <c r="F54" s="138">
         <v>1</v>
       </c>
-      <c r="G54" t="s" s="62">
+      <c r="G54" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H54" t="s" s="66">
+      <c r="H54" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="I54" s="60"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
-      <c r="P54" s="40"/>
-      <c r="Q54" s="40"/>
-      <c r="R54" s="40"/>
-      <c r="S54" s="40"/>
-      <c r="T54" s="41"/>
-    </row>
-    <row r="55" ht="14.5" customHeight="1">
-      <c r="A55" s="61">
+      <c r="I54" s="23"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
+      <c r="T54" s="12"/>
+    </row>
+    <row r="55" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="24">
         <v>46196</v>
       </c>
-      <c r="B55" t="s" s="62">
+      <c r="B55" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C55" t="s" s="63">
+      <c r="C55" s="101" t="s">
         <v>195</v>
       </c>
-      <c r="D55" s="64"/>
-      <c r="E55" s="65"/>
-      <c r="F55" s="81">
+      <c r="D55" s="102"/>
+      <c r="E55" s="103"/>
+      <c r="F55" s="138">
         <v>1</v>
       </c>
-      <c r="G55" s="80">
+      <c r="G55" s="137">
         <v>46025</v>
       </c>
-      <c r="H55" t="s" s="66">
+      <c r="H55" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="I55" s="60"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
-      <c r="N55" s="40"/>
-      <c r="O55" s="40"/>
-      <c r="P55" s="40"/>
-      <c r="Q55" s="40"/>
-      <c r="R55" s="40"/>
-      <c r="S55" s="40"/>
-      <c r="T55" s="41"/>
-    </row>
-    <row r="56" ht="14.5" customHeight="1">
-      <c r="A56" s="67">
+      <c r="I55" s="23"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+      <c r="T55" s="12"/>
+    </row>
+    <row r="56" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="27">
         <v>46197</v>
       </c>
-      <c r="B56" t="s" s="68">
+      <c r="B56" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C56" t="s" s="69">
+      <c r="C56" s="104" t="s">
         <v>197</v>
       </c>
-      <c r="D56" s="70"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="72">
+      <c r="D56" s="105"/>
+      <c r="E56" s="106"/>
+      <c r="F56" s="134">
         <v>2</v>
       </c>
-      <c r="G56" s="79">
+      <c r="G56" s="136">
         <v>46054</v>
       </c>
-      <c r="H56" t="s" s="73">
+      <c r="H56" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="I56" s="60"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="40"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="40"/>
-      <c r="Q56" s="40"/>
-      <c r="R56" s="40"/>
-      <c r="S56" s="40"/>
-      <c r="T56" s="41"/>
-    </row>
-    <row r="57" ht="14.5" customHeight="1">
-      <c r="A57" s="67">
+      <c r="I56" s="23"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
+      <c r="T56" s="12"/>
+    </row>
+    <row r="57" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="27">
         <v>46197</v>
       </c>
-      <c r="B57" t="s" s="68">
+      <c r="B57" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C57" t="s" s="69">
+      <c r="C57" s="104" t="s">
         <v>199</v>
       </c>
-      <c r="D57" s="70"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="72">
+      <c r="D57" s="105"/>
+      <c r="E57" s="106"/>
+      <c r="F57" s="134">
         <v>1</v>
       </c>
-      <c r="G57" t="s" s="68">
+      <c r="G57" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="H57" t="s" s="73">
+      <c r="H57" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="I57" s="60"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="40"/>
-      <c r="N57" s="40"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="40"/>
-      <c r="Q57" s="40"/>
-      <c r="R57" s="40"/>
-      <c r="S57" s="40"/>
-      <c r="T57" s="41"/>
-    </row>
-    <row r="58" ht="14.5" customHeight="1">
-      <c r="A58" s="100"/>
-      <c r="B58" s="101"/>
-      <c r="C58" s="101"/>
-      <c r="D58" s="101"/>
-      <c r="E58" s="101"/>
-      <c r="F58" s="101"/>
-      <c r="G58" s="101"/>
-      <c r="H58" s="102"/>
-      <c r="I58" s="60"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="40"/>
-      <c r="P58" s="40"/>
-      <c r="Q58" s="40"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="40"/>
-      <c r="T58" s="41"/>
-    </row>
-    <row r="59" ht="14.5" customHeight="1">
-      <c r="A59" s="67">
+      <c r="I57" s="23"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="12"/>
+    </row>
+    <row r="58" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="122"/>
+      <c r="B58" s="123"/>
+      <c r="C58" s="123"/>
+      <c r="D58" s="123"/>
+      <c r="E58" s="123"/>
+      <c r="F58" s="123"/>
+      <c r="G58" s="123"/>
+      <c r="H58" s="124"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="11"/>
+      <c r="Q58" s="11"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="11"/>
+      <c r="T58" s="12"/>
+    </row>
+    <row r="59" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="27">
         <v>46197</v>
       </c>
-      <c r="B59" t="s" s="68">
+      <c r="B59" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C59" t="s" s="69">
+      <c r="C59" s="104" t="s">
         <v>201</v>
       </c>
-      <c r="D59" s="70"/>
-      <c r="E59" s="71"/>
-      <c r="F59" s="72">
+      <c r="D59" s="105"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="134">
         <v>1</v>
       </c>
-      <c r="G59" s="79">
+      <c r="G59" s="136">
         <v>46023</v>
       </c>
-      <c r="H59" t="s" s="73">
+      <c r="H59" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="I59" s="60"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="40"/>
-      <c r="Q59" s="40"/>
-      <c r="R59" s="40"/>
-      <c r="S59" s="40"/>
-      <c r="T59" s="41"/>
-    </row>
-    <row r="60" ht="14.5" customHeight="1">
-      <c r="A60" s="67">
+      <c r="I59" s="23"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="11"/>
+      <c r="T59" s="12"/>
+    </row>
+    <row r="60" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="27">
         <v>46197</v>
       </c>
-      <c r="B60" t="s" s="68">
+      <c r="B60" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C60" t="s" s="69">
+      <c r="C60" s="104" t="s">
         <v>203</v>
       </c>
-      <c r="D60" s="70"/>
-      <c r="E60" s="71"/>
-      <c r="F60" s="72">
+      <c r="D60" s="105"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="134">
         <v>1</v>
       </c>
-      <c r="G60" t="s" s="68">
+      <c r="G60" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="H60" t="s" s="73">
+      <c r="H60" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="I60" s="60"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="40"/>
-      <c r="L60" s="40"/>
-      <c r="M60" s="40"/>
-      <c r="N60" s="40"/>
-      <c r="O60" s="40"/>
-      <c r="P60" s="40"/>
-      <c r="Q60" s="40"/>
-      <c r="R60" s="40"/>
-      <c r="S60" s="40"/>
-      <c r="T60" s="41"/>
-    </row>
-    <row r="61" ht="14.5" customHeight="1">
-      <c r="A61" s="61">
+      <c r="I60" s="23"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="11"/>
+      <c r="T60" s="12"/>
+    </row>
+    <row r="61" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="24">
         <v>46198</v>
       </c>
-      <c r="B61" t="s" s="62">
+      <c r="B61" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C61" t="s" s="63">
+      <c r="C61" s="101" t="s">
         <v>205</v>
       </c>
-      <c r="D61" s="64"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="81">
+      <c r="D61" s="102"/>
+      <c r="E61" s="103"/>
+      <c r="F61" s="138">
         <v>2</v>
       </c>
-      <c r="G61" s="80">
+      <c r="G61" s="137">
         <v>46054</v>
       </c>
-      <c r="H61" t="s" s="66">
+      <c r="H61" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="I61" s="60"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="40"/>
-      <c r="L61" s="40"/>
-      <c r="M61" s="40"/>
-      <c r="N61" s="40"/>
-      <c r="O61" s="40"/>
-      <c r="P61" s="40"/>
-      <c r="Q61" s="40"/>
-      <c r="R61" s="40"/>
-      <c r="S61" s="40"/>
-      <c r="T61" s="41"/>
-    </row>
-    <row r="62" ht="14.5" customHeight="1">
-      <c r="A62" s="61">
+      <c r="I61" s="23"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="11"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="11"/>
+      <c r="T61" s="12"/>
+    </row>
+    <row r="62" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="24">
         <v>46198</v>
       </c>
-      <c r="B62" t="s" s="62">
+      <c r="B62" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C62" t="s" s="63">
+      <c r="C62" s="101" t="s">
         <v>207</v>
       </c>
-      <c r="D62" s="64"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="81">
+      <c r="D62" s="102"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="138">
         <v>1</v>
       </c>
-      <c r="G62" t="s" s="62">
+      <c r="G62" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H62" t="s" s="66">
+      <c r="H62" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="I62" s="60"/>
-      <c r="J62" s="40"/>
-      <c r="K62" s="40"/>
-      <c r="L62" s="40"/>
-      <c r="M62" s="40"/>
-      <c r="N62" s="40"/>
-      <c r="O62" s="40"/>
-      <c r="P62" s="40"/>
-      <c r="Q62" s="40"/>
-      <c r="R62" s="40"/>
-      <c r="S62" s="40"/>
-      <c r="T62" s="41"/>
-    </row>
-    <row r="63" ht="14.5" customHeight="1">
-      <c r="A63" s="61">
+      <c r="I62" s="23"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="11"/>
+      <c r="S62" s="11"/>
+      <c r="T62" s="12"/>
+    </row>
+    <row r="63" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="24">
         <v>46198</v>
       </c>
-      <c r="B63" t="s" s="62">
+      <c r="B63" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C63" t="s" s="63">
+      <c r="C63" s="101" t="s">
         <v>209</v>
       </c>
-      <c r="D63" s="64"/>
-      <c r="E63" s="65"/>
-      <c r="F63" t="s" s="62">
+      <c r="D63" s="102"/>
+      <c r="E63" s="103"/>
+      <c r="F63" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G63" s="80">
+      <c r="G63" s="137">
         <v>46054</v>
       </c>
-      <c r="H63" t="s" s="66">
+      <c r="H63" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="I63" s="60"/>
-      <c r="J63" s="40"/>
-      <c r="K63" s="40"/>
-      <c r="L63" s="40"/>
-      <c r="M63" s="40"/>
-      <c r="N63" s="40"/>
-      <c r="O63" s="40"/>
-      <c r="P63" s="40"/>
-      <c r="Q63" s="40"/>
-      <c r="R63" s="40"/>
-      <c r="S63" s="40"/>
-      <c r="T63" s="41"/>
-    </row>
-    <row r="64" ht="14.5" customHeight="1">
-      <c r="A64" s="61">
+      <c r="I63" s="23"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="11"/>
+      <c r="O63" s="11"/>
+      <c r="P63" s="11"/>
+      <c r="Q63" s="11"/>
+      <c r="R63" s="11"/>
+      <c r="S63" s="11"/>
+      <c r="T63" s="12"/>
+    </row>
+    <row r="64" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="24">
         <v>46198</v>
       </c>
-      <c r="B64" t="s" s="62">
+      <c r="B64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C64" t="s" s="63">
+      <c r="C64" s="101" t="s">
         <v>210</v>
       </c>
-      <c r="D64" s="64"/>
-      <c r="E64" s="65"/>
-      <c r="F64" t="s" s="62">
+      <c r="D64" s="102"/>
+      <c r="E64" s="103"/>
+      <c r="F64" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G64" t="s" s="62">
+      <c r="G64" s="133" t="s">
         <v>211</v>
       </c>
-      <c r="H64" t="s" s="66">
+      <c r="H64" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="I64" s="60"/>
-      <c r="J64" s="40"/>
-      <c r="K64" s="40"/>
-      <c r="L64" s="40"/>
-      <c r="M64" s="40"/>
-      <c r="N64" s="40"/>
-      <c r="O64" s="40"/>
-      <c r="P64" s="40"/>
-      <c r="Q64" s="40"/>
-      <c r="R64" s="40"/>
-      <c r="S64" s="40"/>
-      <c r="T64" s="41"/>
-    </row>
-    <row r="65" ht="14.5" customHeight="1">
-      <c r="A65" s="61">
+      <c r="I64" s="23"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="11"/>
+      <c r="O64" s="11"/>
+      <c r="P64" s="11"/>
+      <c r="Q64" s="11"/>
+      <c r="R64" s="11"/>
+      <c r="S64" s="11"/>
+      <c r="T64" s="12"/>
+    </row>
+    <row r="65" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="24">
         <v>46198</v>
       </c>
-      <c r="B65" t="s" s="62">
+      <c r="B65" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C65" t="s" s="63">
+      <c r="C65" s="101" t="s">
         <v>213</v>
       </c>
-      <c r="D65" s="64"/>
-      <c r="E65" s="65"/>
-      <c r="F65" s="81">
+      <c r="D65" s="102"/>
+      <c r="E65" s="103"/>
+      <c r="F65" s="138">
         <v>2</v>
       </c>
-      <c r="G65" s="80">
+      <c r="G65" s="137">
         <v>46082</v>
       </c>
-      <c r="H65" t="s" s="66">
+      <c r="H65" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="I65" s="60"/>
-      <c r="J65" s="40"/>
-      <c r="K65" s="40"/>
-      <c r="L65" s="40"/>
-      <c r="M65" s="40"/>
-      <c r="N65" s="40"/>
-      <c r="O65" s="40"/>
-      <c r="P65" s="40"/>
-      <c r="Q65" s="40"/>
-      <c r="R65" s="40"/>
-      <c r="S65" s="40"/>
-      <c r="T65" s="41"/>
-    </row>
-    <row r="66" ht="14.5" customHeight="1">
-      <c r="A66" s="61">
+      <c r="I65" s="23"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
+      <c r="Q65" s="11"/>
+      <c r="R65" s="11"/>
+      <c r="S65" s="11"/>
+      <c r="T65" s="12"/>
+    </row>
+    <row r="66" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="24">
         <v>46198</v>
       </c>
-      <c r="B66" t="s" s="62">
+      <c r="B66" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C66" t="s" s="63">
+      <c r="C66" s="101" t="s">
         <v>215</v>
       </c>
-      <c r="D66" s="64"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="81">
+      <c r="D66" s="102"/>
+      <c r="E66" s="103"/>
+      <c r="F66" s="138">
         <v>2</v>
       </c>
-      <c r="G66" t="s" s="62">
+      <c r="G66" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="H66" t="s" s="66">
+      <c r="H66" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="I66" s="60"/>
-      <c r="J66" s="40"/>
-      <c r="K66" s="40"/>
-      <c r="L66" s="40"/>
-      <c r="M66" s="40"/>
-      <c r="N66" s="40"/>
-      <c r="O66" s="40"/>
-      <c r="P66" s="40"/>
-      <c r="Q66" s="40"/>
-      <c r="R66" s="40"/>
-      <c r="S66" s="40"/>
-      <c r="T66" s="41"/>
-    </row>
-    <row r="67" ht="14.5" customHeight="1">
-      <c r="A67" s="67">
+      <c r="I66" s="23"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="12"/>
+    </row>
+    <row r="67" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="27">
         <v>46199</v>
       </c>
-      <c r="B67" t="s" s="68">
+      <c r="B67" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C67" t="s" s="69">
+      <c r="C67" s="104" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="70"/>
-      <c r="E67" s="71"/>
-      <c r="F67" s="72">
+      <c r="D67" s="105"/>
+      <c r="E67" s="106"/>
+      <c r="F67" s="134">
         <v>2</v>
       </c>
-      <c r="G67" t="s" s="68">
+      <c r="G67" s="135" t="s">
         <v>81</v>
       </c>
-      <c r="H67" t="s" s="73">
+      <c r="H67" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="I67" s="60"/>
-      <c r="J67" s="40"/>
-      <c r="K67" s="40"/>
-      <c r="L67" s="40"/>
-      <c r="M67" s="40"/>
-      <c r="N67" s="40"/>
-      <c r="O67" s="40"/>
-      <c r="P67" s="40"/>
-      <c r="Q67" s="40"/>
-      <c r="R67" s="40"/>
-      <c r="S67" s="40"/>
-      <c r="T67" s="41"/>
-    </row>
-    <row r="68" ht="14.5" customHeight="1">
-      <c r="A68" s="67">
+      <c r="I67" s="23"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="11"/>
+      <c r="Q67" s="11"/>
+      <c r="R67" s="11"/>
+      <c r="S67" s="11"/>
+      <c r="T67" s="12"/>
+    </row>
+    <row r="68" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="27">
         <v>46199</v>
       </c>
-      <c r="B68" t="s" s="68">
+      <c r="B68" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C68" t="s" s="69">
+      <c r="C68" s="104" t="s">
         <v>219</v>
       </c>
-      <c r="D68" s="70"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="72">
+      <c r="D68" s="105"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="134">
         <v>1</v>
       </c>
-      <c r="G68" s="79">
+      <c r="G68" s="136">
         <v>46055</v>
       </c>
-      <c r="H68" t="s" s="73">
+      <c r="H68" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="I68" s="60"/>
-      <c r="J68" s="40"/>
-      <c r="K68" s="40"/>
-      <c r="L68" s="40"/>
-      <c r="M68" s="40"/>
-      <c r="N68" s="40"/>
-      <c r="O68" s="40"/>
-      <c r="P68" s="40"/>
-      <c r="Q68" s="40"/>
-      <c r="R68" s="40"/>
-      <c r="S68" s="40"/>
-      <c r="T68" s="41"/>
-    </row>
-    <row r="69" ht="14.5" customHeight="1">
-      <c r="A69" s="67">
+      <c r="I68" s="23"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="11"/>
+      <c r="Q68" s="11"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="11"/>
+      <c r="T68" s="12"/>
+    </row>
+    <row r="69" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="27">
         <v>46199</v>
       </c>
-      <c r="B69" t="s" s="68">
+      <c r="B69" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C69" t="s" s="69">
+      <c r="C69" s="104" t="s">
         <v>221</v>
       </c>
-      <c r="D69" s="70"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="72">
+      <c r="D69" s="105"/>
+      <c r="E69" s="106"/>
+      <c r="F69" s="134">
         <v>1</v>
       </c>
-      <c r="G69" s="79">
+      <c r="G69" s="136">
         <v>46024</v>
       </c>
-      <c r="H69" t="s" s="73">
+      <c r="H69" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="I69" s="60"/>
-      <c r="J69" s="40"/>
-      <c r="K69" s="40"/>
-      <c r="L69" s="40"/>
-      <c r="M69" s="40"/>
-      <c r="N69" s="40"/>
-      <c r="O69" s="40"/>
-      <c r="P69" s="40"/>
-      <c r="Q69" s="40"/>
-      <c r="R69" s="40"/>
-      <c r="S69" s="40"/>
-      <c r="T69" s="41"/>
-    </row>
-    <row r="70" ht="14.5" customHeight="1">
-      <c r="A70" s="67">
+      <c r="I69" s="23"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="11"/>
+      <c r="Q69" s="11"/>
+      <c r="R69" s="11"/>
+      <c r="S69" s="11"/>
+      <c r="T69" s="12"/>
+    </row>
+    <row r="70" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="27">
         <v>46199</v>
       </c>
-      <c r="B70" t="s" s="68">
+      <c r="B70" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C70" t="s" s="69">
+      <c r="C70" s="104" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="70"/>
-      <c r="E70" s="71"/>
-      <c r="F70" t="s" s="68">
+      <c r="D70" s="105"/>
+      <c r="E70" s="106"/>
+      <c r="F70" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G70" s="79">
+      <c r="G70" s="136">
         <v>46023</v>
       </c>
-      <c r="H70" t="s" s="73">
+      <c r="H70" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="I70" s="60"/>
-      <c r="J70" s="40"/>
-      <c r="K70" s="40"/>
-      <c r="L70" s="40"/>
-      <c r="M70" s="40"/>
-      <c r="N70" s="40"/>
-      <c r="O70" s="40"/>
-      <c r="P70" s="40"/>
-      <c r="Q70" s="40"/>
-      <c r="R70" s="40"/>
-      <c r="S70" s="40"/>
-      <c r="T70" s="41"/>
-    </row>
-    <row r="71" ht="14.5" customHeight="1">
-      <c r="A71" s="67">
+      <c r="I70" s="23"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="T70" s="12"/>
+    </row>
+    <row r="71" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="27">
         <v>46199</v>
       </c>
-      <c r="B71" t="s" s="68">
+      <c r="B71" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C71" t="s" s="69">
+      <c r="C71" s="104" t="s">
         <v>225</v>
       </c>
-      <c r="D71" s="70"/>
-      <c r="E71" s="71"/>
-      <c r="F71" t="s" s="68">
+      <c r="D71" s="105"/>
+      <c r="E71" s="106"/>
+      <c r="F71" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G71" s="79">
+      <c r="G71" s="136">
         <v>46054</v>
       </c>
-      <c r="H71" t="s" s="73">
+      <c r="H71" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="I71" s="60"/>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
-      <c r="L71" s="40"/>
-      <c r="M71" s="40"/>
-      <c r="N71" s="40"/>
-      <c r="O71" s="40"/>
-      <c r="P71" s="40"/>
-      <c r="Q71" s="40"/>
-      <c r="R71" s="40"/>
-      <c r="S71" s="40"/>
-      <c r="T71" s="41"/>
-    </row>
-    <row r="72" ht="14.5" customHeight="1">
-      <c r="A72" s="67">
+      <c r="I71" s="23"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11"/>
+      <c r="P71" s="11"/>
+      <c r="Q71" s="11"/>
+      <c r="R71" s="11"/>
+      <c r="S71" s="11"/>
+      <c r="T71" s="12"/>
+    </row>
+    <row r="72" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="27">
         <v>46199</v>
       </c>
-      <c r="B72" t="s" s="68">
+      <c r="B72" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C72" t="s" s="69">
+      <c r="C72" s="104" t="s">
         <v>226</v>
       </c>
-      <c r="D72" s="70"/>
-      <c r="E72" s="71"/>
-      <c r="F72" s="72">
+      <c r="D72" s="105"/>
+      <c r="E72" s="106"/>
+      <c r="F72" s="134">
         <v>1</v>
       </c>
-      <c r="G72" t="s" s="68">
+      <c r="G72" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="H72" t="s" s="73">
+      <c r="H72" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="I72" s="60"/>
-      <c r="J72" s="40"/>
-      <c r="K72" s="40"/>
-      <c r="L72" s="40"/>
-      <c r="M72" s="40"/>
-      <c r="N72" s="40"/>
-      <c r="O72" s="40"/>
-      <c r="P72" s="40"/>
-      <c r="Q72" s="40"/>
-      <c r="R72" s="40"/>
-      <c r="S72" s="40"/>
-      <c r="T72" s="41"/>
-    </row>
-    <row r="73" ht="14.5" customHeight="1">
-      <c r="A73" s="61">
+      <c r="I72" s="23"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="11"/>
+      <c r="P72" s="11"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
+      <c r="T72" s="12"/>
+    </row>
+    <row r="73" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="24">
         <v>46200</v>
       </c>
-      <c r="B73" t="s" s="62">
+      <c r="B73" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C73" t="s" s="63">
+      <c r="C73" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="D73" s="64"/>
-      <c r="E73" s="65"/>
-      <c r="F73" t="s" s="62">
+      <c r="D73" s="102"/>
+      <c r="E73" s="103"/>
+      <c r="F73" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G73" s="80">
+      <c r="G73" s="137">
         <v>46082</v>
       </c>
-      <c r="H73" t="s" s="66">
+      <c r="H73" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="I73" s="60"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="40"/>
-      <c r="M73" s="40"/>
-      <c r="N73" s="40"/>
-      <c r="O73" s="40"/>
-      <c r="P73" s="40"/>
-      <c r="Q73" s="40"/>
-      <c r="R73" s="40"/>
-      <c r="S73" s="40"/>
-      <c r="T73" s="41"/>
-    </row>
-    <row r="74" ht="14.5" customHeight="1">
-      <c r="A74" s="61">
+      <c r="I73" s="23"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="11"/>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="11"/>
+      <c r="S73" s="11"/>
+      <c r="T73" s="12"/>
+    </row>
+    <row r="74" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="24">
         <v>46200</v>
       </c>
-      <c r="B74" t="s" s="62">
+      <c r="B74" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C74" t="s" s="63">
+      <c r="C74" s="101" t="s">
         <v>230</v>
       </c>
-      <c r="D74" s="64"/>
-      <c r="E74" s="65"/>
-      <c r="F74" t="s" s="62">
+      <c r="D74" s="102"/>
+      <c r="E74" s="103"/>
+      <c r="F74" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="G74" t="s" s="62">
+      <c r="G74" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H74" t="s" s="66">
+      <c r="H74" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="I74" s="60"/>
-      <c r="J74" s="40"/>
-      <c r="K74" s="40"/>
-      <c r="L74" s="40"/>
-      <c r="M74" s="40"/>
-      <c r="N74" s="40"/>
-      <c r="O74" s="40"/>
-      <c r="P74" s="40"/>
-      <c r="Q74" s="40"/>
-      <c r="R74" s="40"/>
-      <c r="S74" s="40"/>
-      <c r="T74" s="41"/>
-    </row>
-    <row r="75" ht="14.5" customHeight="1">
-      <c r="A75" s="61">
+      <c r="I74" s="23"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="11"/>
+      <c r="T74" s="12"/>
+    </row>
+    <row r="75" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="24">
         <v>46200</v>
       </c>
-      <c r="B75" t="s" s="62">
+      <c r="B75" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C75" t="s" s="63">
+      <c r="C75" s="101" t="s">
         <v>232</v>
       </c>
-      <c r="D75" s="64"/>
-      <c r="E75" s="65"/>
-      <c r="F75" s="81">
+      <c r="D75" s="102"/>
+      <c r="E75" s="103"/>
+      <c r="F75" s="138">
         <v>1</v>
       </c>
-      <c r="G75" t="s" s="62">
+      <c r="G75" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H75" t="s" s="66">
+      <c r="H75" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="I75" s="60"/>
-      <c r="J75" s="40"/>
-      <c r="K75" s="40"/>
-      <c r="L75" s="40"/>
-      <c r="M75" s="40"/>
-      <c r="N75" s="40"/>
-      <c r="O75" s="40"/>
-      <c r="P75" s="40"/>
-      <c r="Q75" s="40"/>
-      <c r="R75" s="40"/>
-      <c r="S75" s="40"/>
-      <c r="T75" s="41"/>
-    </row>
-    <row r="76" ht="14.5" customHeight="1">
-      <c r="A76" s="61">
+      <c r="I75" s="23"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="11"/>
+      <c r="Q75" s="11"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="11"/>
+      <c r="T75" s="12"/>
+    </row>
+    <row r="76" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="24">
         <v>46200</v>
       </c>
-      <c r="B76" t="s" s="62">
+      <c r="B76" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C76" t="s" s="63">
+      <c r="C76" s="101" t="s">
         <v>234</v>
       </c>
-      <c r="D76" s="64"/>
-      <c r="E76" s="65"/>
-      <c r="F76" s="81">
+      <c r="D76" s="102"/>
+      <c r="E76" s="103"/>
+      <c r="F76" s="138">
         <v>2</v>
       </c>
-      <c r="G76" t="s" s="62">
+      <c r="G76" s="133" t="s">
         <v>81</v>
       </c>
-      <c r="H76" t="s" s="66">
+      <c r="H76" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="I76" s="60"/>
-      <c r="J76" s="40"/>
-      <c r="K76" s="40"/>
-      <c r="L76" s="40"/>
-      <c r="M76" s="40"/>
-      <c r="N76" s="40"/>
-      <c r="O76" s="40"/>
-      <c r="P76" s="40"/>
-      <c r="Q76" s="40"/>
-      <c r="R76" s="40"/>
-      <c r="S76" s="40"/>
-      <c r="T76" s="41"/>
-    </row>
-    <row r="77" ht="14.5" customHeight="1">
-      <c r="A77" s="61">
+      <c r="I76" s="23"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="11"/>
+      <c r="Q76" s="11"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="12"/>
+    </row>
+    <row r="77" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="24">
         <v>46200</v>
       </c>
-      <c r="B77" t="s" s="62">
+      <c r="B77" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C77" t="s" s="63">
+      <c r="C77" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="65"/>
-      <c r="F77" s="81">
+      <c r="D77" s="102"/>
+      <c r="E77" s="103"/>
+      <c r="F77" s="138">
         <v>2</v>
       </c>
-      <c r="G77" t="s" s="62">
+      <c r="G77" s="133" t="s">
         <v>237</v>
       </c>
-      <c r="H77" t="s" s="66">
+      <c r="H77" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="I77" s="60"/>
-      <c r="J77" s="40"/>
-      <c r="K77" s="40"/>
-      <c r="L77" s="40"/>
-      <c r="M77" s="40"/>
-      <c r="N77" s="40"/>
-      <c r="O77" s="40"/>
-      <c r="P77" s="40"/>
-      <c r="Q77" s="40"/>
-      <c r="R77" s="40"/>
-      <c r="S77" s="40"/>
-      <c r="T77" s="41"/>
-    </row>
-    <row r="78" ht="14.5" customHeight="1">
-      <c r="A78" s="61">
+      <c r="I77" s="23"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="11"/>
+      <c r="O77" s="11"/>
+      <c r="P77" s="11"/>
+      <c r="Q77" s="11"/>
+      <c r="R77" s="11"/>
+      <c r="S77" s="11"/>
+      <c r="T77" s="12"/>
+    </row>
+    <row r="78" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="24">
         <v>46200</v>
       </c>
-      <c r="B78" t="s" s="62">
+      <c r="B78" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C78" t="s" s="63">
+      <c r="C78" s="101" t="s">
         <v>238</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="65"/>
-      <c r="F78" s="81">
+      <c r="D78" s="102"/>
+      <c r="E78" s="103"/>
+      <c r="F78" s="138">
         <v>1</v>
       </c>
-      <c r="G78" s="80">
+      <c r="G78" s="137">
         <v>46024</v>
       </c>
-      <c r="H78" t="s" s="66">
+      <c r="H78" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="I78" s="60"/>
-      <c r="J78" s="40"/>
-      <c r="K78" s="40"/>
-      <c r="L78" s="40"/>
-      <c r="M78" s="40"/>
-      <c r="N78" s="40"/>
-      <c r="O78" s="40"/>
-      <c r="P78" s="40"/>
-      <c r="Q78" s="40"/>
-      <c r="R78" s="40"/>
-      <c r="S78" s="40"/>
-      <c r="T78" s="41"/>
-    </row>
-    <row r="79" ht="14.5" customHeight="1">
-      <c r="A79" s="67">
+      <c r="I78" s="23"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="11"/>
+      <c r="O78" s="11"/>
+      <c r="P78" s="11"/>
+      <c r="Q78" s="11"/>
+      <c r="R78" s="11"/>
+      <c r="S78" s="11"/>
+      <c r="T78" s="12"/>
+    </row>
+    <row r="79" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="27">
         <v>46201</v>
       </c>
-      <c r="B79" t="s" s="68">
+      <c r="B79" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C79" t="s" s="69">
+      <c r="C79" s="104" t="s">
         <v>239</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="71"/>
-      <c r="F79" s="72">
+      <c r="D79" s="105"/>
+      <c r="E79" s="106"/>
+      <c r="F79" s="134">
         <v>2</v>
       </c>
-      <c r="G79" s="79">
+      <c r="G79" s="136">
         <v>46082</v>
       </c>
-      <c r="H79" t="s" s="73">
+      <c r="H79" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="I79" s="60"/>
-      <c r="J79" s="40"/>
-      <c r="K79" s="40"/>
-      <c r="L79" s="40"/>
-      <c r="M79" s="40"/>
-      <c r="N79" s="40"/>
-      <c r="O79" s="40"/>
-      <c r="P79" s="40"/>
-      <c r="Q79" s="40"/>
-      <c r="R79" s="40"/>
-      <c r="S79" s="40"/>
-      <c r="T79" s="41"/>
-    </row>
-    <row r="80" ht="14.5" customHeight="1">
-      <c r="A80" s="67">
+      <c r="I79" s="23"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="11"/>
+      <c r="O79" s="11"/>
+      <c r="P79" s="11"/>
+      <c r="Q79" s="11"/>
+      <c r="R79" s="11"/>
+      <c r="S79" s="11"/>
+      <c r="T79" s="12"/>
+    </row>
+    <row r="80" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="27">
         <v>46201</v>
       </c>
-      <c r="B80" t="s" s="68">
+      <c r="B80" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C80" t="s" s="69">
+      <c r="C80" s="104" t="s">
         <v>241</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="72">
+      <c r="D80" s="105"/>
+      <c r="E80" s="106"/>
+      <c r="F80" s="134">
         <v>2</v>
       </c>
-      <c r="G80" t="s" s="68">
+      <c r="G80" s="135" t="s">
         <v>144</v>
       </c>
-      <c r="H80" t="s" s="73">
+      <c r="H80" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="I80" s="60"/>
-      <c r="J80" s="40"/>
-      <c r="K80" s="40"/>
-      <c r="L80" s="40"/>
-      <c r="M80" s="40"/>
-      <c r="N80" s="40"/>
-      <c r="O80" s="40"/>
-      <c r="P80" s="40"/>
-      <c r="Q80" s="40"/>
-      <c r="R80" s="40"/>
-      <c r="S80" s="40"/>
-      <c r="T80" s="41"/>
-    </row>
-    <row r="81" ht="14.5" customHeight="1">
-      <c r="A81" s="67">
+      <c r="I80" s="23"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="11"/>
+      <c r="O80" s="11"/>
+      <c r="P80" s="11"/>
+      <c r="Q80" s="11"/>
+      <c r="R80" s="11"/>
+      <c r="S80" s="11"/>
+      <c r="T80" s="12"/>
+    </row>
+    <row r="81" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="27">
         <v>46201</v>
       </c>
-      <c r="B81" t="s" s="68">
+      <c r="B81" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C81" t="s" s="69">
+      <c r="C81" s="104" t="s">
         <v>243</v>
       </c>
-      <c r="D81" s="70"/>
-      <c r="E81" s="71"/>
-      <c r="F81" s="72">
+      <c r="D81" s="105"/>
+      <c r="E81" s="106"/>
+      <c r="F81" s="134">
         <v>2</v>
       </c>
-      <c r="G81" t="s" s="68">
+      <c r="G81" s="135" t="s">
         <v>244</v>
       </c>
-      <c r="H81" t="s" s="73">
+      <c r="H81" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="I81" s="60"/>
-      <c r="J81" s="40"/>
-      <c r="K81" s="40"/>
-      <c r="L81" s="40"/>
-      <c r="M81" s="40"/>
-      <c r="N81" s="40"/>
-      <c r="O81" s="40"/>
-      <c r="P81" s="40"/>
-      <c r="Q81" s="40"/>
-      <c r="R81" s="40"/>
-      <c r="S81" s="40"/>
-      <c r="T81" s="41"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="103">
+      <c r="I81" s="23"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="11"/>
+      <c r="O81" s="11"/>
+      <c r="P81" s="11"/>
+      <c r="Q81" s="11"/>
+      <c r="R81" s="11"/>
+      <c r="S81" s="11"/>
+      <c r="T81" s="12"/>
+    </row>
+    <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="33">
         <v>46201</v>
       </c>
-      <c r="B82" t="s" s="104">
+      <c r="B82" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="C82" t="s" s="105">
+      <c r="C82" s="129" t="s">
         <v>246</v>
       </c>
-      <c r="D82" s="106"/>
-      <c r="E82" s="107"/>
-      <c r="F82" t="s" s="104">
+      <c r="D82" s="130"/>
+      <c r="E82" s="131"/>
+      <c r="F82" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="G82" s="108">
+      <c r="G82" s="140">
         <v>46023</v>
       </c>
-      <c r="H82" t="s" s="109">
+      <c r="H82" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="I82" s="110"/>
-      <c r="J82" s="111"/>
-      <c r="K82" s="111"/>
-      <c r="L82" s="111"/>
-      <c r="M82" s="111"/>
-      <c r="N82" s="111"/>
-      <c r="O82" s="111"/>
-      <c r="P82" s="111"/>
-      <c r="Q82" s="111"/>
-      <c r="R82" s="111"/>
-      <c r="S82" s="111"/>
-      <c r="T82" s="112"/>
+      <c r="I82" s="36"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="37"/>
+      <c r="L82" s="37"/>
+      <c r="M82" s="37"/>
+      <c r="N82" s="37"/>
+      <c r="O82" s="37"/>
+      <c r="P82" s="37"/>
+      <c r="Q82" s="37"/>
+      <c r="R82" s="37"/>
+      <c r="S82" s="37"/>
+      <c r="T82" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A5:T6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="J7:Q7"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="L24:P25"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M28:P29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="M30:P31"/>
-    <mergeCell ref="L33:P33"/>
-    <mergeCell ref="L34:P35"/>
-    <mergeCell ref="L37:P37"/>
-    <mergeCell ref="L38:P39"/>
-    <mergeCell ref="L41:P41"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="L42:P43"/>
-    <mergeCell ref="L45:P45"/>
-    <mergeCell ref="L46:P47"/>
-    <mergeCell ref="L49:P49"/>
-    <mergeCell ref="L50:P51"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C2:F2"/>
@@ -7448,73 +7584,142 @@
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="L42:P43"/>
+    <mergeCell ref="L45:P45"/>
+    <mergeCell ref="L46:P47"/>
+    <mergeCell ref="L49:P49"/>
+    <mergeCell ref="L50:P51"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="L33:P33"/>
+    <mergeCell ref="L34:P35"/>
+    <mergeCell ref="L37:P37"/>
+    <mergeCell ref="L38:P39"/>
+    <mergeCell ref="L41:P41"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="L24:P25"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M28:P29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="M30:P31"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="A5:T6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="J7:Q7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
   </mergeCells>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F32 F34:F57 F59:F82">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F32 F34:F57 F59:F82" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"1,X,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:Q10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:Q10" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Repubblica Ceca,Corea del Sud,Messico,Sud Africa"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L11:Q11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L11:Q11" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Bosnia Erzegovina,Canada,Qatar,Svizzera"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:Q12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:Q12" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"Brazil,Haiti,Marocco,Scozia"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L13:Q13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L13:Q13" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Australia,Paraguay,Turchia,USA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14:Q14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14:Q14" xr:uid="{00000000-0002-0000-0200-000005000000}">
       <formula1>"Costa d'Avorio,Curaçao,Ecuador,Germania"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L15:Q15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L15:Q15" xr:uid="{00000000-0002-0000-0200-000006000000}">
       <formula1>"Giappone,Olanda,Tunisia,Svezia"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L16:Q16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L16:Q16" xr:uid="{00000000-0002-0000-0200-000007000000}">
       <formula1>"Belgio,Egitto,Iran,Nuova Zelanda"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L17:Q17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L17:Q17" xr:uid="{00000000-0002-0000-0200-000008000000}">
       <formula1>"Capo Verde,Arabia Saudita,Spagna,Uruguay"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L18:Q18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L18:Q18" xr:uid="{00000000-0002-0000-0200-000009000000}">
       <formula1>"Francia,Iraq,Norvegia,Senegal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L19:Q19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L19:Q19" xr:uid="{00000000-0002-0000-0200-00000A000000}">
       <formula1>"Algeria,Argentina,Austria,Giordania"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L20:Q20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L20:Q20" xr:uid="{00000000-0002-0000-0200-00000B000000}">
       <formula1>"Colombia,Congo DR,Portogallo,Uzbekistan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L21:Q21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L21:Q21" xr:uid="{00000000-0002-0000-0200-00000C000000}">
       <formula1>"Croazia,Inghilterra,Ghana,Panama"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -7522,367 +7727,367 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:C63"/>
-  <sheetFormatPr defaultColWidth="13.3333" defaultRowHeight="17.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C63"/>
+  <sheetFormatPr defaultColWidth="13.36328125" defaultRowHeight="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="13.3516" style="113" customWidth="1"/>
-    <col min="4" max="16384" width="13.3516" style="113" customWidth="1"/>
+    <col min="1" max="4" width="13.36328125" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="13.36328125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.35" customHeight="1">
-      <c r="A1" t="s" s="114">
+    <row r="1" spans="1:3" ht="12.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="132" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-    </row>
-    <row r="2" ht="15.3" customHeight="1">
-      <c r="A2" t="s" s="115">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="B2" t="s" s="116">
+      <c r="B2" s="40" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="3" ht="15.3" customHeight="1">
-      <c r="A3" t="s" s="117">
+    <row r="3" spans="1:3" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="B3" t="s" s="118">
+      <c r="B3" s="42" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="4" ht="15.05" customHeight="1">
-      <c r="B4" t="s" s="119">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="43" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="5" ht="15.05" customHeight="1">
-      <c r="B5" t="s" s="119">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="43" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="6" ht="15.05" customHeight="1">
-      <c r="B6" t="s" s="119">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="43" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="7" ht="13.3" customHeight="1">
-      <c r="A7" t="s" s="120">
+    <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="44" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="8" ht="15.3" customHeight="1">
-      <c r="A8" t="s" s="121">
+    <row r="8" spans="1:3" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="B8" t="s" s="122">
+      <c r="B8" s="46" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="9" ht="15.05" customHeight="1">
-      <c r="B9" t="s" s="119">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="43" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="B10" t="s" s="119">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="43" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="11" ht="15.05" customHeight="1">
-      <c r="B11" t="s" s="119">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="43" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="13.3" customHeight="1">
-      <c r="A12" t="s" s="120">
+    <row r="12" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="44" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="13" ht="15.3" customHeight="1">
-      <c r="A13" t="s" s="121">
+    <row r="13" spans="1:3" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="45" t="s">
         <v>263</v>
       </c>
-      <c r="B13" t="s" s="122">
+      <c r="B13" s="46" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" ht="15.05" customHeight="1">
-      <c r="B14" t="s" s="119">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="43" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="15" ht="15.05" customHeight="1">
-      <c r="B15" t="s" s="119">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="43" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="16" ht="15.05" customHeight="1">
-      <c r="B16" t="s" s="119">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="43" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="17" ht="13.3" customHeight="1">
-      <c r="A17" t="s" s="120">
+    <row r="17" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="44" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="18" ht="15.3" customHeight="1">
-      <c r="A18" t="s" s="121">
+    <row r="18" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="45" t="s">
         <v>267</v>
       </c>
-      <c r="B18" t="s" s="122">
+      <c r="B18" s="46" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="19" ht="15.05" customHeight="1">
-      <c r="B19" t="s" s="119">
+    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="43" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="B20" t="s" s="119">
+    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="43" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="21" ht="15.05" customHeight="1">
-      <c r="B21" t="s" s="119">
+    <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" ht="13.3" customHeight="1">
-      <c r="A22" t="s" s="120">
+    <row r="22" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="44" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="23" ht="15.3" customHeight="1">
-      <c r="A23" t="s" s="121">
+    <row r="23" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="45" t="s">
         <v>271</v>
       </c>
-      <c r="B23" t="s" s="122">
+      <c r="B23" s="46" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="24" ht="15.05" customHeight="1">
-      <c r="B24" t="s" s="119">
+    <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="43" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="25" ht="15.05" customHeight="1">
-      <c r="B25" t="s" s="119">
+    <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="43" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="26" ht="15.05" customHeight="1">
-      <c r="B26" t="s" s="119">
+    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="43" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="27" ht="13.3" customHeight="1">
-      <c r="A27" t="s" s="120">
+    <row r="27" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="44" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="28" ht="15.3" customHeight="1">
-      <c r="A28" t="s" s="121">
+    <row r="28" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="B28" t="s" s="122">
+      <c r="B28" s="46" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="29" ht="15.05" customHeight="1">
-      <c r="B29" t="s" s="119">
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="43" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="30" ht="15.05" customHeight="1">
-      <c r="B30" t="s" s="119">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="43" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="31" ht="15.05" customHeight="1">
-      <c r="B31" t="s" s="119">
+    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="43" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="32" ht="13.3" customHeight="1">
-      <c r="A32" t="s" s="120">
+    <row r="32" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="44" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="33" ht="15.3" customHeight="1">
-      <c r="A33" t="s" s="121">
+    <row r="33" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="B33" t="s" s="122">
+      <c r="B33" s="46" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="34" ht="15.05" customHeight="1">
-      <c r="B34" t="s" s="119">
+    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="43" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="35" ht="15.05" customHeight="1">
-      <c r="B35" t="s" s="119">
+    <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="43" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="36" ht="15.05" customHeight="1">
-      <c r="B36" t="s" s="119">
+    <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="43" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="37" ht="13.3" customHeight="1">
-      <c r="A37" t="s" s="120">
+    <row r="37" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="44" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="38" ht="15.3" customHeight="1">
-      <c r="A38" t="s" s="121">
+    <row r="38" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="B38" t="s" s="122">
+      <c r="B38" s="46" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="39" ht="15.05" customHeight="1">
-      <c r="B39" t="s" s="119">
+    <row r="39" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="43" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="40" ht="15.05" customHeight="1">
-      <c r="B40" t="s" s="119">
+    <row r="40" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="43" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="41" ht="15.05" customHeight="1">
-      <c r="B41" t="s" s="119">
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="43" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="42" ht="13.3" customHeight="1">
-      <c r="A42" t="s" s="120">
+    <row r="42" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="44" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="43" ht="15.3" customHeight="1">
-      <c r="A43" t="s" s="121">
+    <row r="43" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="45" t="s">
         <v>290</v>
       </c>
-      <c r="B43" t="s" s="122">
+      <c r="B43" s="46" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="44" ht="15.05" customHeight="1">
-      <c r="B44" t="s" s="119">
+    <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="43" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="45" ht="15.05" customHeight="1">
-      <c r="B45" t="s" s="119">
+    <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="43" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="46" ht="15.05" customHeight="1">
-      <c r="B46" t="s" s="119">
+    <row r="46" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="43" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" ht="13.3" customHeight="1">
-      <c r="A47" t="s" s="120">
+    <row r="47" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="44" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="48" ht="15.3" customHeight="1">
-      <c r="A48" t="s" s="121">
+    <row r="48" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="B48" t="s" s="122">
+      <c r="B48" s="46" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="49" ht="15.05" customHeight="1">
-      <c r="B49" t="s" s="119">
+    <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="43" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="50" ht="15.05" customHeight="1">
-      <c r="B50" t="s" s="119">
+    <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="43" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" ht="15.05" customHeight="1">
-      <c r="B51" t="s" s="119">
+    <row r="51" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="43" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="52" ht="13.3" customHeight="1">
-      <c r="A52" t="s" s="120">
+    <row r="52" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="44" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="53" ht="15.3" customHeight="1">
-      <c r="A53" t="s" s="121">
+    <row r="53" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="45" t="s">
         <v>297</v>
       </c>
-      <c r="B53" t="s" s="122">
+      <c r="B53" s="46" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="54" ht="15.05" customHeight="1">
-      <c r="B54" t="s" s="119">
+    <row r="54" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="43" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="55" ht="15.05" customHeight="1">
-      <c r="B55" t="s" s="119">
+    <row r="55" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="43" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="56" ht="15.05" customHeight="1">
-      <c r="B56" t="s" s="119">
+    <row r="56" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="43" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="57" ht="13.3" customHeight="1">
-      <c r="A57" t="s" s="120">
+    <row r="57" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="44" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="58" ht="15.3" customHeight="1">
-      <c r="A58" t="s" s="121">
+    <row r="58" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="45" t="s">
         <v>301</v>
       </c>
-      <c r="B58" t="s" s="122">
+      <c r="B58" s="46" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="59" ht="15.05" customHeight="1">
-      <c r="B59" t="s" s="119">
+    <row r="59" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="43" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="60" ht="15.05" customHeight="1">
-      <c r="B60" t="s" s="119">
+    <row r="60" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="43" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="61" ht="15.05" customHeight="1">
-      <c r="B61" t="s" s="119">
+    <row r="61" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="43" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="62" ht="13.3" customHeight="1">
-      <c r="A62" t="s" s="123">
+    <row r="62" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="47" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="63" ht="15.3" customHeight="1">
-      <c r="A63" t="s" s="124">
+    <row r="63" spans="1:2" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="48" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7891,7 +8096,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -7899,268 +8104,269 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A80"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.5" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B80"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.8516" style="125" customWidth="1"/>
-    <col min="2" max="16384" width="8.85156" style="125" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" hidden="1">
-      <c r="A1" t="s" s="126">
+    <row r="1" spans="1:2" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="B1" t="s" s="127">
+      <c r="B1" s="50" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" hidden="1">
-      <c r="A2" s="128"/>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" hidden="1">
-      <c r="A3" s="128"/>
-    </row>
-    <row r="4" ht="14.5" customHeight="1" hidden="1">
-      <c r="A4" s="128"/>
-    </row>
-    <row r="5" ht="14.5" customHeight="1" hidden="1">
-      <c r="A5" s="128"/>
-    </row>
-    <row r="6" ht="14.5" customHeight="1" hidden="1">
-      <c r="A6" s="128"/>
-    </row>
-    <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="129"/>
-    </row>
-    <row r="8" ht="14.5" customHeight="1">
-      <c r="A8" s="130"/>
-    </row>
-    <row r="9" ht="14.5" customHeight="1">
-      <c r="A9" s="130"/>
-    </row>
-    <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="130"/>
-    </row>
-    <row r="11" ht="14.5" customHeight="1">
-      <c r="A11" s="130"/>
-    </row>
-    <row r="12" ht="14.5" customHeight="1">
-      <c r="A12" s="130"/>
-    </row>
-    <row r="13" ht="14.5" customHeight="1">
-      <c r="A13" s="130"/>
-    </row>
-    <row r="14" ht="14.5" customHeight="1">
-      <c r="A14" s="130"/>
-    </row>
-    <row r="15" ht="14.5" customHeight="1">
-      <c r="A15" s="130"/>
-    </row>
-    <row r="16" ht="14.5" customHeight="1">
-      <c r="A16" s="130"/>
-    </row>
-    <row r="17" ht="14.5" customHeight="1">
-      <c r="A17" s="130"/>
-    </row>
-    <row r="18" ht="14.5" customHeight="1">
-      <c r="A18" s="130"/>
-    </row>
-    <row r="19" ht="14.5" customHeight="1">
-      <c r="A19" s="130"/>
-    </row>
-    <row r="20" ht="14.5" customHeight="1">
-      <c r="A20" s="130"/>
-    </row>
-    <row r="21" ht="14.5" customHeight="1">
-      <c r="A21" s="130"/>
-    </row>
-    <row r="22" ht="14.5" customHeight="1">
-      <c r="A22" s="130"/>
-    </row>
-    <row r="23" ht="14.5" customHeight="1">
-      <c r="A23" s="130"/>
-    </row>
-    <row r="24" ht="14.5" customHeight="1">
-      <c r="A24" s="130"/>
-    </row>
-    <row r="25" ht="14.5" customHeight="1">
-      <c r="A25" s="130"/>
-    </row>
-    <row r="26" ht="14.5" customHeight="1">
-      <c r="A26" s="130"/>
-    </row>
-    <row r="27" ht="14.5" customHeight="1">
-      <c r="A27" s="130"/>
-    </row>
-    <row r="28" ht="14.5" customHeight="1">
-      <c r="A28" s="130"/>
-    </row>
-    <row r="29" ht="14.5" customHeight="1">
-      <c r="A29" s="130"/>
-    </row>
-    <row r="30" ht="14.5" customHeight="1">
-      <c r="A30" s="130"/>
-    </row>
-    <row r="31" ht="14.5" customHeight="1">
-      <c r="A31" s="130"/>
-    </row>
-    <row r="32" ht="14.5" customHeight="1">
-      <c r="A32" s="130"/>
-    </row>
-    <row r="33" ht="14.5" customHeight="1">
-      <c r="A33" s="130"/>
-    </row>
-    <row r="34" ht="14.5" customHeight="1">
-      <c r="A34" s="130"/>
-    </row>
-    <row r="35" ht="14.5" customHeight="1">
-      <c r="A35" s="130"/>
-    </row>
-    <row r="36" ht="14.5" customHeight="1">
-      <c r="A36" s="130"/>
-    </row>
-    <row r="37" ht="14.5" customHeight="1">
-      <c r="A37" s="130"/>
-    </row>
-    <row r="38" ht="14.5" customHeight="1">
-      <c r="A38" s="130"/>
-    </row>
-    <row r="39" ht="14.5" customHeight="1">
-      <c r="A39" s="130"/>
-    </row>
-    <row r="40" ht="14.5" customHeight="1">
-      <c r="A40" s="130"/>
-    </row>
-    <row r="41" ht="14.5" customHeight="1">
-      <c r="A41" s="130"/>
-    </row>
-    <row r="42" ht="14.5" customHeight="1">
-      <c r="A42" s="130"/>
-    </row>
-    <row r="43" ht="14.5" customHeight="1">
-      <c r="A43" s="130"/>
-    </row>
-    <row r="44" ht="14.5" customHeight="1">
-      <c r="A44" s="130"/>
-    </row>
-    <row r="45" ht="14.5" customHeight="1">
-      <c r="A45" s="130"/>
-    </row>
-    <row r="46" ht="14.5" customHeight="1">
-      <c r="A46" s="130"/>
-    </row>
-    <row r="47" ht="14.5" customHeight="1">
-      <c r="A47" s="130"/>
-    </row>
-    <row r="48" ht="14.5" customHeight="1">
-      <c r="A48" s="130"/>
-    </row>
-    <row r="49" ht="14.5" customHeight="1">
-      <c r="A49" s="130"/>
-    </row>
-    <row r="50" ht="14.5" customHeight="1">
-      <c r="A50" s="130"/>
-    </row>
-    <row r="51" ht="14.5" customHeight="1">
-      <c r="A51" s="130"/>
-    </row>
-    <row r="52" ht="14.5" customHeight="1">
-      <c r="A52" s="130"/>
-    </row>
-    <row r="53" ht="14.5" customHeight="1">
-      <c r="A53" s="130"/>
-    </row>
-    <row r="54" ht="14.5" customHeight="1">
-      <c r="A54" s="130"/>
-    </row>
-    <row r="55" ht="14.5" customHeight="1">
-      <c r="A55" s="130"/>
-    </row>
-    <row r="56" ht="14.5" customHeight="1">
-      <c r="A56" s="130"/>
-    </row>
-    <row r="57" ht="14.5" customHeight="1">
-      <c r="A57" s="130"/>
-    </row>
-    <row r="58" ht="14.5" customHeight="1">
-      <c r="A58" s="130"/>
-    </row>
-    <row r="59" ht="14.5" customHeight="1">
-      <c r="A59" s="130"/>
-    </row>
-    <row r="60" ht="14.5" customHeight="1">
-      <c r="A60" s="130"/>
-    </row>
-    <row r="61" ht="14.5" customHeight="1">
-      <c r="A61" s="130"/>
-    </row>
-    <row r="62" ht="14.5" customHeight="1">
-      <c r="A62" s="130"/>
-    </row>
-    <row r="63" ht="14.5" customHeight="1">
-      <c r="A63" s="131"/>
-    </row>
-    <row r="64" ht="14.5" customHeight="1">
-      <c r="A64" s="132"/>
-    </row>
-    <row r="65" ht="14.5" customHeight="1">
-      <c r="A65" s="130"/>
-    </row>
-    <row r="66" ht="14.5" customHeight="1">
-      <c r="A66" s="130"/>
-    </row>
-    <row r="67" ht="14.5" customHeight="1">
-      <c r="A67" s="130"/>
-    </row>
-    <row r="68" ht="14.5" customHeight="1">
-      <c r="A68" s="130"/>
-    </row>
-    <row r="69" ht="14.5" customHeight="1">
-      <c r="A69" s="130"/>
-    </row>
-    <row r="70" ht="14.5" customHeight="1">
-      <c r="A70" s="130"/>
-    </row>
-    <row r="71" ht="14.5" customHeight="1">
-      <c r="A71" s="130"/>
-    </row>
-    <row r="72" ht="14.5" customHeight="1">
-      <c r="A72" s="130"/>
-    </row>
-    <row r="73" ht="14.5" customHeight="1">
-      <c r="A73" s="130"/>
-    </row>
-    <row r="74" ht="14.5" customHeight="1">
-      <c r="A74" s="130"/>
-    </row>
-    <row r="75" ht="14.5" customHeight="1">
-      <c r="A75" s="130"/>
-    </row>
-    <row r="76" ht="14.5" customHeight="1">
-      <c r="A76" s="130"/>
-    </row>
-    <row r="77" ht="14.5" customHeight="1">
-      <c r="A77" s="130"/>
-    </row>
-    <row r="78" ht="14.5" customHeight="1">
-      <c r="A78" s="133">
+    <row r="2" spans="1:2" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="51"/>
+    </row>
+    <row r="3" spans="1:2" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="51"/>
+    </row>
+    <row r="4" spans="1:2" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="51"/>
+    </row>
+    <row r="5" spans="1:2" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="51"/>
+    </row>
+    <row r="6" spans="1:2" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="51"/>
+    </row>
+    <row r="7" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="52"/>
+    </row>
+    <row r="8" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="53"/>
+    </row>
+    <row r="9" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="53"/>
+    </row>
+    <row r="10" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="53"/>
+    </row>
+    <row r="11" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="53"/>
+    </row>
+    <row r="12" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="53"/>
+    </row>
+    <row r="13" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="53"/>
+    </row>
+    <row r="14" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="53"/>
+    </row>
+    <row r="15" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="53"/>
+    </row>
+    <row r="16" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="53"/>
+    </row>
+    <row r="17" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="53"/>
+    </row>
+    <row r="18" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="53"/>
+    </row>
+    <row r="19" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="53"/>
+    </row>
+    <row r="20" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="53"/>
+    </row>
+    <row r="21" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="53"/>
+    </row>
+    <row r="22" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="53"/>
+    </row>
+    <row r="23" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="53"/>
+    </row>
+    <row r="24" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="53"/>
+    </row>
+    <row r="25" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="53"/>
+    </row>
+    <row r="26" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="53"/>
+    </row>
+    <row r="27" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="53"/>
+    </row>
+    <row r="28" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="53"/>
+    </row>
+    <row r="29" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="53"/>
+    </row>
+    <row r="30" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="53"/>
+    </row>
+    <row r="31" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="53"/>
+    </row>
+    <row r="32" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="53"/>
+    </row>
+    <row r="33" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="53"/>
+    </row>
+    <row r="34" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="53"/>
+    </row>
+    <row r="35" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="53"/>
+    </row>
+    <row r="36" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="53"/>
+    </row>
+    <row r="37" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+    </row>
+    <row r="38" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="53"/>
+    </row>
+    <row r="39" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="53"/>
+    </row>
+    <row r="40" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="53"/>
+    </row>
+    <row r="41" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="53"/>
+    </row>
+    <row r="42" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="53"/>
+    </row>
+    <row r="43" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="53"/>
+    </row>
+    <row r="44" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="53"/>
+    </row>
+    <row r="45" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="53"/>
+    </row>
+    <row r="46" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="53"/>
+    </row>
+    <row r="47" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="53"/>
+    </row>
+    <row r="48" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="53"/>
+    </row>
+    <row r="49" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="53"/>
+    </row>
+    <row r="50" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="53"/>
+    </row>
+    <row r="51" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="53"/>
+    </row>
+    <row r="52" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="53"/>
+    </row>
+    <row r="53" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="53"/>
+    </row>
+    <row r="54" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="53"/>
+    </row>
+    <row r="55" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="53"/>
+    </row>
+    <row r="56" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="53"/>
+    </row>
+    <row r="57" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="53"/>
+    </row>
+    <row r="58" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="53"/>
+    </row>
+    <row r="59" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="53"/>
+    </row>
+    <row r="60" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="53"/>
+    </row>
+    <row r="61" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="53"/>
+    </row>
+    <row r="62" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="53"/>
+    </row>
+    <row r="63" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="54"/>
+    </row>
+    <row r="64" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="55"/>
+    </row>
+    <row r="65" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="53"/>
+    </row>
+    <row r="66" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="53"/>
+    </row>
+    <row r="67" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="53"/>
+    </row>
+    <row r="68" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="53"/>
+    </row>
+    <row r="69" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="53"/>
+    </row>
+    <row r="70" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="53"/>
+    </row>
+    <row r="71" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="53"/>
+    </row>
+    <row r="72" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="53"/>
+    </row>
+    <row r="73" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="53"/>
+    </row>
+    <row r="74" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="53"/>
+    </row>
+    <row r="75" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="53"/>
+    </row>
+    <row r="76" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="53"/>
+    </row>
+    <row r="77" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="53"/>
+    </row>
+    <row r="78" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="56">
         <v>1</v>
       </c>
     </row>
-    <row r="79" ht="14.5" customHeight="1">
-      <c r="A79" t="s" s="134">
+    <row r="79" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="57" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="80" ht="14.5" customHeight="1">
-      <c r="A80" s="135">
+    <row r="80" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="58">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/data/pronostici/TOTOMONDIALE2026_Salvatore_Scala.xlsx
+++ b/data/pronostici/TOTOMONDIALE2026_Salvatore_Scala.xlsx
@@ -1930,20 +1930,224 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1967,212 +2171,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2184,20 +2184,166 @@
         <b/>
         <color rgb="FF000000"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
       <border>
         <left style="thin">
           <color indexed="22"/>
         </left>
         <right style="thin">
-          <color indexed="22"/>
+          <color indexed="24"/>
         </right>
         <top style="thin">
-          <color indexed="13"/>
+          <color indexed="24"/>
         </top>
         <bottom style="thin">
-          <color indexed="28"/>
+          <color indexed="24"/>
         </bottom>
         <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
+          <color indexed="24"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="24"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="23"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="22"/>
+        </left>
+        <right style="thin">
+          <color indexed="24"/>
+        </right>
+        <top style="thin">
+          <color indexed="24"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="24"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="23"/>
+        </left>
+        <right style="thin">
+          <color indexed="23"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color indexed="13"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="23"/>
+        </left>
+        <right style="thin">
+          <color indexed="23"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color indexed="13"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="27"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color indexed="23"/>
+        </left>
+        <right style="thin">
+          <color indexed="23"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color indexed="13"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="23"/>
+        </vertical>
         <horizontal/>
       </border>
     </dxf>
@@ -2329,90 +2475,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="27"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="22"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="22"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="22"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
           <bgColor indexed="18"/>
         </patternFill>
       </fill>
@@ -2468,84 +2530,22 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="21"/>
-        </patternFill>
-      </fill>
       <border>
         <left style="thin">
-          <color indexed="23"/>
+          <color indexed="22"/>
         </left>
         <right style="thin">
-          <color indexed="23"/>
+          <color indexed="22"/>
         </right>
-        <top/>
-        <bottom style="medium">
+        <top style="thin">
           <color indexed="13"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="28"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="23"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="21"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="23"/>
-        </left>
-        <right style="thin">
-          <color indexed="23"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color indexed="13"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="23"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="27"/>
-          <bgColor indexed="21"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="23"/>
-        </left>
-        <right style="thin">
-          <color indexed="23"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color indexed="13"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="23"/>
-        </vertical>
+        <vertical/>
         <horizontal/>
       </border>
     </dxf>
@@ -2609,21 +2609,21 @@
     <tableStyle name="PivotStyleCustom01" count="17" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="0"/>
-      <tableStyleElement type="firstColumn" dxfId="11"/>
-      <tableStyleElement type="lastColumn" dxfId="10"/>
-      <tableStyleElement type="firstSubtotalColumn" dxfId="6"/>
-      <tableStyleElement type="secondSubtotalColumn" dxfId="5"/>
-      <tableStyleElement type="thirdSubtotalColumn" dxfId="4"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="3"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="2"/>
-      <tableStyleElement type="thirdSubtotalRow" dxfId="1"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="14"/>
-      <tableStyleElement type="secondColumnSubheading" dxfId="13"/>
-      <tableStyleElement type="thirdColumnSubheading" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="9"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="8"/>
-      <tableStyleElement type="thirdRowSubheading" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstSubtotalColumn" dxfId="11"/>
+      <tableStyleElement type="secondSubtotalColumn" dxfId="10"/>
+      <tableStyleElement type="thirdSubtotalColumn" dxfId="9"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="8"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="7"/>
+      <tableStyleElement type="thirdSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumnSubheading" dxfId="5"/>
+      <tableStyleElement type="secondColumnSubheading" dxfId="4"/>
+      <tableStyleElement type="thirdColumnSubheading" dxfId="3"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="2"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="1"/>
+      <tableStyleElement type="thirdRowSubheading" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -4326,11 +4326,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
     </row>
     <row r="7" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
@@ -4426,273 +4426,247 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="135"/>
     </row>
     <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="70" t="s">
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="71"/>
+      <c r="F2" s="139"/>
     </row>
     <row r="3" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="61" t="s">
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="62"/>
+      <c r="F3" s="129"/>
     </row>
     <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="61" t="s">
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="62"/>
+      <c r="F4" s="129"/>
     </row>
     <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="61" t="s">
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="62"/>
+      <c r="F5" s="129"/>
     </row>
     <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="72"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="74"/>
+      <c r="A6" s="130"/>
+      <c r="B6" s="131"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="132"/>
     </row>
     <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="61" t="s">
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="62"/>
+      <c r="F7" s="129"/>
     </row>
     <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="61" t="s">
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="62"/>
+      <c r="F8" s="129"/>
     </row>
     <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="61" t="s">
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="62"/>
+      <c r="F9" s="129"/>
     </row>
     <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="72"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="74"/>
+      <c r="A10" s="130"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="132"/>
     </row>
     <row r="11" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="61" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="62"/>
+      <c r="F11" s="129"/>
     </row>
     <row r="12" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="61" t="s">
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="62"/>
+      <c r="F12" s="129"/>
     </row>
     <row r="13" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="61" t="s">
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="62"/>
+      <c r="F13" s="129"/>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
+      <c r="A14" s="130"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="132"/>
     </row>
     <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="61" t="s">
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="62"/>
+      <c r="F15" s="129"/>
     </row>
     <row r="16" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="61" t="s">
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="62"/>
+      <c r="F16" s="129"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="61" t="s">
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="62"/>
+      <c r="F17" s="129"/>
     </row>
     <row r="18" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="61" t="s">
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="62"/>
+      <c r="F18" s="129"/>
     </row>
     <row r="19" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="61" t="s">
+      <c r="B19" s="127"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="62"/>
+      <c r="F19" s="129"/>
     </row>
     <row r="20" spans="1:6" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="77"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="119"/>
     </row>
     <row r="21" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="78"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="80"/>
+      <c r="A21" s="120"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="122"/>
     </row>
     <row r="22" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="81"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="83"/>
+      <c r="A22" s="123"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A20:F22"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
@@ -4702,6 +4676,32 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -4750,16 +4750,16 @@
       <c r="T1" s="9"/>
     </row>
     <row r="2" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127" t="s">
+      <c r="B2" s="77"/>
+      <c r="C2" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
       <c r="G2" s="10"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -4776,16 +4776,16 @@
       <c r="T2" s="12"/>
     </row>
     <row r="3" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="127" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
       <c r="G3" s="10"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
@@ -4824,73 +4824,73 @@
       <c r="T4" s="12"/>
     </row>
     <row r="5" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="86"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="105"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="87"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="86"/>
+      <c r="A6" s="106"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="107"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="104"/>
+      <c r="S6" s="104"/>
+      <c r="T6" s="105"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="95"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="114"/>
       <c r="I7" s="17"/>
-      <c r="J7" s="93" t="s">
+      <c r="J7" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="95"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="113"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="114"/>
       <c r="R7" s="18"/>
       <c r="S7" s="15"/>
       <c r="T7" s="16"/>
@@ -4902,11 +4902,11 @@
       <c r="B8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="108" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
+      <c r="D8" s="109"/>
+      <c r="E8" s="109"/>
       <c r="F8" s="20" t="s">
         <v>43</v>
       </c>
@@ -4917,16 +4917,16 @@
         <v>12</v>
       </c>
       <c r="I8" s="22"/>
-      <c r="J8" s="91" t="s">
+      <c r="J8" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="92"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="109"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="111"/>
       <c r="R8" s="23"/>
       <c r="S8" s="11"/>
       <c r="T8" s="12"/>
@@ -4938,35 +4938,35 @@
       <c r="B9" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="101" t="s">
+      <c r="C9" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="102"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="133" t="s">
+      <c r="D9" s="68"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="133" t="s">
+      <c r="G9" s="59" t="s">
         <v>49</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>50</v>
       </c>
       <c r="I9" s="22"/>
-      <c r="J9" s="91" t="s">
+      <c r="J9" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="90"/>
-      <c r="L9" s="89" t="s">
+      <c r="K9" s="109"/>
+      <c r="L9" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="89" t="s">
+      <c r="M9" s="109"/>
+      <c r="N9" s="109"/>
+      <c r="O9" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="92"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="111"/>
       <c r="R9" s="23"/>
       <c r="S9" s="11"/>
       <c r="T9" s="12"/>
@@ -4978,35 +4978,35 @@
       <c r="B10" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="104" t="s">
+      <c r="C10" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="134">
+      <c r="D10" s="71"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="60">
         <v>1</v>
       </c>
-      <c r="G10" s="135" t="s">
+      <c r="G10" s="61" t="s">
         <v>55</v>
       </c>
       <c r="H10" s="29" t="s">
         <v>56</v>
       </c>
       <c r="I10" s="22"/>
-      <c r="J10" s="96" t="s">
+      <c r="J10" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="97"/>
+      <c r="K10" s="100"/>
       <c r="L10" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="99"/>
-      <c r="N10" s="99"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
       <c r="O10" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="100"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="82"/>
       <c r="R10" s="23"/>
       <c r="S10" s="11"/>
       <c r="T10" s="12"/>
@@ -5018,35 +5018,35 @@
       <c r="B11" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="134">
+      <c r="D11" s="71"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="60">
         <v>2</v>
       </c>
-      <c r="G11" s="136">
+      <c r="G11" s="62">
         <v>46054</v>
       </c>
       <c r="H11" s="29" t="s">
         <v>61</v>
       </c>
       <c r="I11" s="22"/>
-      <c r="J11" s="96" t="s">
+      <c r="J11" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="97"/>
+      <c r="K11" s="100"/>
       <c r="L11" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="81"/>
       <c r="O11" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="100"/>
+      <c r="P11" s="81"/>
+      <c r="Q11" s="82"/>
       <c r="R11" s="23"/>
       <c r="S11" s="11"/>
       <c r="T11" s="12"/>
@@ -5058,35 +5058,35 @@
       <c r="B12" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="102"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="133" t="s">
+      <c r="D12" s="68"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="137">
+      <c r="G12" s="63">
         <v>46023</v>
       </c>
       <c r="H12" s="26" t="s">
         <v>66</v>
       </c>
       <c r="I12" s="22"/>
-      <c r="J12" s="96" t="s">
+      <c r="J12" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="K12" s="97"/>
+      <c r="K12" s="100"/>
       <c r="L12" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="99"/>
-      <c r="N12" s="99"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="81"/>
       <c r="O12" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="100"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="82"/>
       <c r="R12" s="23"/>
       <c r="S12" s="11"/>
       <c r="T12" s="12"/>
@@ -5098,35 +5098,35 @@
       <c r="B13" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="102"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="138">
+      <c r="D13" s="68"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="64">
         <v>2</v>
       </c>
-      <c r="G13" s="133" t="s">
+      <c r="G13" s="59" t="s">
         <v>71</v>
       </c>
       <c r="H13" s="26" t="s">
         <v>72</v>
       </c>
       <c r="I13" s="22"/>
-      <c r="J13" s="96" t="s">
+      <c r="J13" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="97"/>
+      <c r="K13" s="100"/>
       <c r="L13" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
       <c r="O13" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="100"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="82"/>
       <c r="R13" s="23"/>
       <c r="S13" s="11"/>
       <c r="T13" s="12"/>
@@ -5138,35 +5138,35 @@
       <c r="B14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="105"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="134">
+      <c r="D14" s="71"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="60">
         <v>1</v>
       </c>
-      <c r="G14" s="136">
+      <c r="G14" s="62">
         <v>46025</v>
       </c>
       <c r="H14" s="29" t="s">
         <v>76</v>
       </c>
       <c r="I14" s="22"/>
-      <c r="J14" s="96" t="s">
+      <c r="J14" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="97"/>
+      <c r="K14" s="100"/>
       <c r="L14" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="M14" s="99"/>
-      <c r="N14" s="99"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="81"/>
       <c r="O14" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="100"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="82"/>
       <c r="R14" s="23"/>
       <c r="S14" s="11"/>
       <c r="T14" s="12"/>
@@ -5178,35 +5178,35 @@
       <c r="B15" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="105"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="134">
+      <c r="D15" s="71"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="60">
         <v>2</v>
       </c>
-      <c r="G15" s="135" t="s">
+      <c r="G15" s="61" t="s">
         <v>81</v>
       </c>
       <c r="H15" s="29" t="s">
         <v>82</v>
       </c>
       <c r="I15" s="22"/>
-      <c r="J15" s="96" t="s">
+      <c r="J15" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="97"/>
+      <c r="K15" s="100"/>
       <c r="L15" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="M15" s="99"/>
-      <c r="N15" s="99"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
       <c r="O15" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="100"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="82"/>
       <c r="R15" s="23"/>
       <c r="S15" s="11"/>
       <c r="T15" s="12"/>
@@ -5218,35 +5218,35 @@
       <c r="B16" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="105"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="134">
+      <c r="D16" s="71"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="60">
         <v>2</v>
       </c>
-      <c r="G16" s="136">
+      <c r="G16" s="62">
         <v>46023</v>
       </c>
       <c r="H16" s="29" t="s">
         <v>87</v>
       </c>
       <c r="I16" s="22"/>
-      <c r="J16" s="96" t="s">
+      <c r="J16" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="K16" s="97"/>
+      <c r="K16" s="100"/>
       <c r="L16" s="98" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="99"/>
-      <c r="N16" s="99"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="81"/>
       <c r="O16" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="100"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="82"/>
       <c r="R16" s="23"/>
       <c r="S16" s="11"/>
       <c r="T16" s="12"/>
@@ -5258,35 +5258,35 @@
       <c r="B17" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="105"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="134">
+      <c r="D17" s="71"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="60">
         <v>1</v>
       </c>
-      <c r="G17" s="135" t="s">
+      <c r="G17" s="61" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>93</v>
       </c>
       <c r="I17" s="22"/>
-      <c r="J17" s="96" t="s">
+      <c r="J17" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="K17" s="97"/>
+      <c r="K17" s="100"/>
       <c r="L17" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="81"/>
       <c r="O17" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="100"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="82"/>
       <c r="R17" s="23"/>
       <c r="S17" s="11"/>
       <c r="T17" s="12"/>
@@ -5298,35 +5298,35 @@
       <c r="B18" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="135" t="s">
+      <c r="D18" s="71"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="136">
+      <c r="G18" s="62">
         <v>46024</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>98</v>
       </c>
       <c r="I18" s="22"/>
-      <c r="J18" s="96" t="s">
+      <c r="J18" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="K18" s="97"/>
+      <c r="K18" s="100"/>
       <c r="L18" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="M18" s="99"/>
-      <c r="N18" s="99"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
       <c r="O18" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="100"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="82"/>
       <c r="R18" s="23"/>
       <c r="S18" s="11"/>
       <c r="T18" s="12"/>
@@ -5338,35 +5338,35 @@
       <c r="B19" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="102"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="133" t="s">
+      <c r="D19" s="68"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="137">
+      <c r="G19" s="63">
         <v>46023</v>
       </c>
       <c r="H19" s="26" t="s">
         <v>103</v>
       </c>
       <c r="I19" s="22"/>
-      <c r="J19" s="96" t="s">
+      <c r="J19" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="K19" s="97"/>
+      <c r="K19" s="100"/>
       <c r="L19" s="98" t="s">
         <v>105</v>
       </c>
-      <c r="M19" s="99"/>
-      <c r="N19" s="99"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="81"/>
       <c r="O19" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="100"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="82"/>
       <c r="R19" s="23"/>
       <c r="S19" s="11"/>
       <c r="T19" s="12"/>
@@ -5378,35 +5378,35 @@
       <c r="B20" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="101" t="s">
+      <c r="C20" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="138">
+      <c r="D20" s="68"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="64">
         <v>1</v>
       </c>
-      <c r="G20" s="133" t="s">
+      <c r="G20" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H20" s="26" t="s">
         <v>108</v>
       </c>
       <c r="I20" s="22"/>
-      <c r="J20" s="96" t="s">
+      <c r="J20" s="95" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="97"/>
+      <c r="K20" s="100"/>
       <c r="L20" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="M20" s="99"/>
-      <c r="N20" s="99"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="81"/>
       <c r="O20" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="P20" s="99"/>
-      <c r="Q20" s="100"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="82"/>
       <c r="R20" s="23"/>
       <c r="S20" s="11"/>
       <c r="T20" s="12"/>
@@ -5418,35 +5418,35 @@
       <c r="B21" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="101" t="s">
+      <c r="C21" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="138">
+      <c r="D21" s="68"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="64">
         <v>1</v>
       </c>
-      <c r="G21" s="133" t="s">
+      <c r="G21" s="59" t="s">
         <v>113</v>
       </c>
       <c r="H21" s="26" t="s">
         <v>114</v>
       </c>
       <c r="I21" s="22"/>
-      <c r="J21" s="110" t="s">
+      <c r="J21" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="K21" s="111"/>
-      <c r="L21" s="107" t="s">
+      <c r="K21" s="102"/>
+      <c r="L21" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="108"/>
-      <c r="N21" s="108"/>
-      <c r="O21" s="107" t="s">
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="P21" s="108"/>
-      <c r="Q21" s="109"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="85"/>
       <c r="R21" s="23"/>
       <c r="S21" s="11"/>
       <c r="T21" s="12"/>
@@ -5458,15 +5458,15 @@
       <c r="B22" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="101" t="s">
+      <c r="C22" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="138">
+      <c r="D22" s="68"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="64">
         <v>1</v>
       </c>
-      <c r="G22" s="137">
+      <c r="G22" s="63">
         <v>46025</v>
       </c>
       <c r="H22" s="26" t="s">
@@ -5492,15 +5492,15 @@
       <c r="B23" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="105"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="134">
+      <c r="D23" s="71"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="60">
         <v>2</v>
       </c>
-      <c r="G23" s="135" t="s">
+      <c r="G23" s="61" t="s">
         <v>71</v>
       </c>
       <c r="H23" s="29" t="s">
@@ -5509,13 +5509,13 @@
       <c r="I23" s="23"/>
       <c r="J23" s="11"/>
       <c r="K23" s="32"/>
-      <c r="L23" s="112" t="s">
+      <c r="L23" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="114"/>
+      <c r="M23" s="87"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="87"/>
+      <c r="P23" s="88"/>
       <c r="Q23" s="23"/>
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
@@ -5528,15 +5528,15 @@
       <c r="B24" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="104" t="s">
+      <c r="C24" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="105"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="134">
+      <c r="D24" s="71"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="60">
         <v>1</v>
       </c>
-      <c r="G24" s="135" t="s">
+      <c r="G24" s="61" t="s">
         <v>49</v>
       </c>
       <c r="H24" s="29" t="s">
@@ -5545,13 +5545,13 @@
       <c r="I24" s="23"/>
       <c r="J24" s="11"/>
       <c r="K24" s="32"/>
-      <c r="L24" s="115" t="s">
+      <c r="L24" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="M24" s="99"/>
-      <c r="N24" s="99"/>
-      <c r="O24" s="99"/>
-      <c r="P24" s="100"/>
+      <c r="M24" s="81"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="82"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
@@ -5564,15 +5564,15 @@
       <c r="B25" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="104" t="s">
+      <c r="C25" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="105"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="134">
+      <c r="D25" s="71"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="60">
         <v>1</v>
       </c>
-      <c r="G25" s="136">
+      <c r="G25" s="62">
         <v>46025</v>
       </c>
       <c r="H25" s="29" t="s">
@@ -5581,11 +5581,11 @@
       <c r="I25" s="23"/>
       <c r="J25" s="11"/>
       <c r="K25" s="32"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="108"/>
-      <c r="N25" s="108"/>
-      <c r="O25" s="108"/>
-      <c r="P25" s="109"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="85"/>
       <c r="Q25" s="23"/>
       <c r="R25" s="11"/>
       <c r="S25" s="11"/>
@@ -5598,15 +5598,15 @@
       <c r="B26" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="101" t="s">
+      <c r="C26" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="102"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="138">
+      <c r="D26" s="68"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="64">
         <v>2</v>
       </c>
-      <c r="G26" s="133" t="s">
+      <c r="G26" s="59" t="s">
         <v>71</v>
       </c>
       <c r="H26" s="26" t="s">
@@ -5632,15 +5632,15 @@
       <c r="B27" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="102"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="138">
+      <c r="D27" s="68"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="64">
         <v>1</v>
       </c>
-      <c r="G27" s="133" t="s">
+      <c r="G27" s="59" t="s">
         <v>130</v>
       </c>
       <c r="H27" s="26" t="s">
@@ -5649,13 +5649,13 @@
       <c r="I27" s="23"/>
       <c r="J27" s="11"/>
       <c r="K27" s="32"/>
-      <c r="L27" s="112" t="s">
+      <c r="L27" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="M27" s="113"/>
-      <c r="N27" s="113"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="114"/>
+      <c r="M27" s="87"/>
+      <c r="N27" s="87"/>
+      <c r="O27" s="87"/>
+      <c r="P27" s="88"/>
       <c r="Q27" s="23"/>
       <c r="R27" s="11"/>
       <c r="S27" s="11"/>
@@ -5668,15 +5668,15 @@
       <c r="B28" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="101" t="s">
+      <c r="C28" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="102"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="138">
+      <c r="D28" s="68"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="64">
         <v>1</v>
       </c>
-      <c r="G28" s="133" t="s">
+      <c r="G28" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H28" s="26" t="s">
@@ -5685,15 +5685,15 @@
       <c r="I28" s="23"/>
       <c r="J28" s="11"/>
       <c r="K28" s="32"/>
-      <c r="L28" s="96" t="s">
+      <c r="L28" s="95" t="s">
         <v>135</v>
       </c>
       <c r="M28" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="100"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="82"/>
       <c r="Q28" s="23"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
@@ -5706,15 +5706,15 @@
       <c r="B29" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="102"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="138">
+      <c r="D29" s="68"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="64">
         <v>1</v>
       </c>
-      <c r="G29" s="133" t="s">
+      <c r="G29" s="59" t="s">
         <v>113</v>
       </c>
       <c r="H29" s="26" t="s">
@@ -5723,11 +5723,11 @@
       <c r="I29" s="23"/>
       <c r="J29" s="11"/>
       <c r="K29" s="32"/>
-      <c r="L29" s="117"/>
-      <c r="M29" s="99"/>
-      <c r="N29" s="99"/>
-      <c r="O29" s="99"/>
-      <c r="P29" s="100"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="81"/>
+      <c r="P29" s="82"/>
       <c r="Q29" s="23"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
@@ -5740,15 +5740,15 @@
       <c r="B30" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="101" t="s">
+      <c r="C30" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="102"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="133" t="s">
+      <c r="D30" s="68"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="137">
+      <c r="G30" s="63">
         <v>46055</v>
       </c>
       <c r="H30" s="26" t="s">
@@ -5757,15 +5757,15 @@
       <c r="I30" s="23"/>
       <c r="J30" s="11"/>
       <c r="K30" s="32"/>
-      <c r="L30" s="96" t="s">
+      <c r="L30" s="95" t="s">
         <v>141</v>
       </c>
       <c r="M30" s="98" t="s">
         <v>142</v>
       </c>
-      <c r="N30" s="99"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="100"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="81"/>
+      <c r="P30" s="82"/>
       <c r="Q30" s="23"/>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
@@ -5778,15 +5778,15 @@
       <c r="B31" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="104" t="s">
+      <c r="C31" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="105"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="135" t="s">
+      <c r="D31" s="71"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G31" s="135" t="s">
+      <c r="G31" s="61" t="s">
         <v>144</v>
       </c>
       <c r="H31" s="29" t="s">
@@ -5795,11 +5795,11 @@
       <c r="I31" s="23"/>
       <c r="J31" s="11"/>
       <c r="K31" s="32"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="108"/>
-      <c r="N31" s="108"/>
-      <c r="O31" s="108"/>
-      <c r="P31" s="109"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="85"/>
       <c r="Q31" s="23"/>
       <c r="R31" s="11"/>
       <c r="S31" s="11"/>
@@ -5812,15 +5812,15 @@
       <c r="B32" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="104" t="s">
+      <c r="C32" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="105"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="134">
+      <c r="D32" s="71"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="60">
         <v>2</v>
       </c>
-      <c r="G32" s="136">
+      <c r="G32" s="62">
         <v>46054</v>
       </c>
       <c r="H32" s="29" t="s">
@@ -5840,24 +5840,24 @@
       <c r="T32" s="12"/>
     </row>
     <row r="33" spans="1:20" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="119"/>
-      <c r="B33" s="120"/>
-      <c r="C33" s="120"/>
-      <c r="D33" s="120"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="120"/>
-      <c r="H33" s="121"/>
+      <c r="A33" s="92"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="94"/>
       <c r="I33" s="23"/>
       <c r="J33" s="11"/>
       <c r="K33" s="32"/>
-      <c r="L33" s="112" t="s">
+      <c r="L33" s="86" t="s">
         <v>148</v>
       </c>
-      <c r="M33" s="113"/>
-      <c r="N33" s="113"/>
-      <c r="O33" s="113"/>
-      <c r="P33" s="114"/>
+      <c r="M33" s="87"/>
+      <c r="N33" s="87"/>
+      <c r="O33" s="87"/>
+      <c r="P33" s="88"/>
       <c r="Q33" s="23"/>
       <c r="R33" s="11"/>
       <c r="S33" s="11"/>
@@ -5870,15 +5870,15 @@
       <c r="B34" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="104" t="s">
+      <c r="C34" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="105"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="135" t="s">
+      <c r="D34" s="71"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="136">
+      <c r="G34" s="62">
         <v>46023</v>
       </c>
       <c r="H34" s="29" t="s">
@@ -5887,13 +5887,13 @@
       <c r="I34" s="23"/>
       <c r="J34" s="11"/>
       <c r="K34" s="32"/>
-      <c r="L34" s="115" t="s">
+      <c r="L34" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="99"/>
-      <c r="P34" s="100"/>
+      <c r="M34" s="81"/>
+      <c r="N34" s="81"/>
+      <c r="O34" s="81"/>
+      <c r="P34" s="82"/>
       <c r="Q34" s="23"/>
       <c r="R34" s="11"/>
       <c r="S34" s="11"/>
@@ -5906,15 +5906,15 @@
       <c r="B35" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="104" t="s">
+      <c r="C35" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="D35" s="105"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="135" t="s">
+      <c r="D35" s="71"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G35" s="136">
+      <c r="G35" s="62">
         <v>46054</v>
       </c>
       <c r="H35" s="29" t="s">
@@ -5923,11 +5923,11 @@
       <c r="I35" s="23"/>
       <c r="J35" s="11"/>
       <c r="K35" s="32"/>
-      <c r="L35" s="116"/>
-      <c r="M35" s="108"/>
-      <c r="N35" s="108"/>
-      <c r="O35" s="108"/>
-      <c r="P35" s="109"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="84"/>
+      <c r="N35" s="84"/>
+      <c r="O35" s="84"/>
+      <c r="P35" s="85"/>
       <c r="Q35" s="23"/>
       <c r="R35" s="11"/>
       <c r="S35" s="11"/>
@@ -5940,15 +5940,15 @@
       <c r="B36" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="101" t="s">
+      <c r="C36" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="102"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="138">
+      <c r="D36" s="68"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="64">
         <v>1</v>
       </c>
-      <c r="G36" s="133" t="s">
+      <c r="G36" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H36" s="26" t="s">
@@ -5974,15 +5974,15 @@
       <c r="B37" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="101" t="s">
+      <c r="C37" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="D37" s="102"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="133" t="s">
+      <c r="D37" s="68"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G37" s="133" t="s">
+      <c r="G37" s="59" t="s">
         <v>49</v>
       </c>
       <c r="H37" s="26" t="s">
@@ -5991,13 +5991,13 @@
       <c r="I37" s="23"/>
       <c r="J37" s="11"/>
       <c r="K37" s="32"/>
-      <c r="L37" s="112" t="s">
+      <c r="L37" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="M37" s="113"/>
-      <c r="N37" s="113"/>
-      <c r="O37" s="113"/>
-      <c r="P37" s="114"/>
+      <c r="M37" s="87"/>
+      <c r="N37" s="87"/>
+      <c r="O37" s="87"/>
+      <c r="P37" s="88"/>
       <c r="Q37" s="23"/>
       <c r="R37" s="11"/>
       <c r="S37" s="11"/>
@@ -6010,15 +6010,15 @@
       <c r="B38" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="101" t="s">
+      <c r="C38" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="102"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="138">
+      <c r="D38" s="68"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="64">
         <v>1</v>
       </c>
-      <c r="G38" s="137">
+      <c r="G38" s="63">
         <v>46023</v>
       </c>
       <c r="H38" s="26" t="s">
@@ -6027,13 +6027,13 @@
       <c r="I38" s="23"/>
       <c r="J38" s="11"/>
       <c r="K38" s="32"/>
-      <c r="L38" s="115" t="s">
+      <c r="L38" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="M38" s="99"/>
-      <c r="N38" s="99"/>
-      <c r="O38" s="99"/>
-      <c r="P38" s="100"/>
+      <c r="M38" s="81"/>
+      <c r="N38" s="81"/>
+      <c r="O38" s="81"/>
+      <c r="P38" s="82"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="11"/>
       <c r="S38" s="11"/>
@@ -6046,15 +6046,15 @@
       <c r="B39" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="104" t="s">
+      <c r="C39" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="105"/>
-      <c r="E39" s="106"/>
-      <c r="F39" s="135" t="s">
+      <c r="D39" s="71"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G39" s="136">
+      <c r="G39" s="62">
         <v>46055</v>
       </c>
       <c r="H39" s="29" t="s">
@@ -6063,11 +6063,11 @@
       <c r="I39" s="23"/>
       <c r="J39" s="11"/>
       <c r="K39" s="32"/>
-      <c r="L39" s="116"/>
-      <c r="M39" s="108"/>
-      <c r="N39" s="108"/>
-      <c r="O39" s="108"/>
-      <c r="P39" s="109"/>
+      <c r="L39" s="83"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
+      <c r="O39" s="84"/>
+      <c r="P39" s="85"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="11"/>
       <c r="S39" s="11"/>
@@ -6080,15 +6080,15 @@
       <c r="B40" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="104" t="s">
+      <c r="C40" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="105"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="134">
+      <c r="D40" s="71"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="60">
         <v>1</v>
       </c>
-      <c r="G40" s="135" t="s">
+      <c r="G40" s="61" t="s">
         <v>92</v>
       </c>
       <c r="H40" s="29" t="s">
@@ -6114,15 +6114,15 @@
       <c r="B41" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="104" t="s">
+      <c r="C41" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="D41" s="105"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="134">
+      <c r="D41" s="71"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="60">
         <v>1</v>
       </c>
-      <c r="G41" s="136">
+      <c r="G41" s="62">
         <v>46024</v>
       </c>
       <c r="H41" s="29" t="s">
@@ -6131,13 +6131,13 @@
       <c r="I41" s="23"/>
       <c r="J41" s="11"/>
       <c r="K41" s="32"/>
-      <c r="L41" s="112" t="s">
+      <c r="L41" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="M41" s="113"/>
-      <c r="N41" s="113"/>
-      <c r="O41" s="113"/>
-      <c r="P41" s="114"/>
+      <c r="M41" s="87"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="87"/>
+      <c r="P41" s="88"/>
       <c r="Q41" s="23"/>
       <c r="R41" s="11"/>
       <c r="S41" s="11"/>
@@ -6150,15 +6150,15 @@
       <c r="B42" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="104" t="s">
+      <c r="C42" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="105"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="134">
+      <c r="D42" s="71"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="60">
         <v>1</v>
       </c>
-      <c r="G42" s="136">
+      <c r="G42" s="62">
         <v>46025</v>
       </c>
       <c r="H42" s="29" t="s">
@@ -6167,13 +6167,13 @@
       <c r="I42" s="23"/>
       <c r="J42" s="11"/>
       <c r="K42" s="32"/>
-      <c r="L42" s="115" t="s">
+      <c r="L42" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="M42" s="99"/>
-      <c r="N42" s="99"/>
-      <c r="O42" s="99"/>
-      <c r="P42" s="100"/>
+      <c r="M42" s="81"/>
+      <c r="N42" s="81"/>
+      <c r="O42" s="81"/>
+      <c r="P42" s="82"/>
       <c r="Q42" s="23"/>
       <c r="R42" s="11"/>
       <c r="S42" s="11"/>
@@ -6186,15 +6186,15 @@
       <c r="B43" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="104" t="s">
+      <c r="C43" s="70" t="s">
         <v>169</v>
       </c>
-      <c r="D43" s="105"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="134">
+      <c r="D43" s="71"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="60">
         <v>1</v>
       </c>
-      <c r="G43" s="136">
+      <c r="G43" s="62">
         <v>46024</v>
       </c>
       <c r="H43" s="29" t="s">
@@ -6203,11 +6203,11 @@
       <c r="I43" s="23"/>
       <c r="J43" s="11"/>
       <c r="K43" s="32"/>
-      <c r="L43" s="116"/>
-      <c r="M43" s="108"/>
-      <c r="N43" s="108"/>
-      <c r="O43" s="108"/>
-      <c r="P43" s="109"/>
+      <c r="L43" s="83"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="85"/>
       <c r="Q43" s="23"/>
       <c r="R43" s="11"/>
       <c r="S43" s="11"/>
@@ -6220,15 +6220,15 @@
       <c r="B44" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="101" t="s">
+      <c r="C44" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="102"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="138">
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="64">
         <v>1</v>
       </c>
-      <c r="G44" s="133" t="s">
+      <c r="G44" s="59" t="s">
         <v>130</v>
       </c>
       <c r="H44" s="26" t="s">
@@ -6254,15 +6254,15 @@
       <c r="B45" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="101" t="s">
+      <c r="C45" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="102"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="138">
+      <c r="D45" s="68"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="64">
         <v>2</v>
       </c>
-      <c r="G45" s="133" t="s">
+      <c r="G45" s="59" t="s">
         <v>71</v>
       </c>
       <c r="H45" s="26" t="s">
@@ -6271,13 +6271,13 @@
       <c r="I45" s="23"/>
       <c r="J45" s="11"/>
       <c r="K45" s="32"/>
-      <c r="L45" s="112" t="s">
+      <c r="L45" s="86" t="s">
         <v>175</v>
       </c>
-      <c r="M45" s="113"/>
-      <c r="N45" s="113"/>
-      <c r="O45" s="113"/>
-      <c r="P45" s="114"/>
+      <c r="M45" s="87"/>
+      <c r="N45" s="87"/>
+      <c r="O45" s="87"/>
+      <c r="P45" s="88"/>
       <c r="Q45" s="23"/>
       <c r="R45" s="11"/>
       <c r="S45" s="11"/>
@@ -6290,15 +6290,15 @@
       <c r="B46" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="101" t="s">
+      <c r="C46" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="D46" s="102"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="138">
+      <c r="D46" s="68"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="64">
         <v>1</v>
       </c>
-      <c r="G46" s="133" t="s">
+      <c r="G46" s="59" t="s">
         <v>113</v>
       </c>
       <c r="H46" s="26" t="s">
@@ -6307,13 +6307,13 @@
       <c r="I46" s="23"/>
       <c r="J46" s="11"/>
       <c r="K46" s="32"/>
-      <c r="L46" s="115" t="s">
+      <c r="L46" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="M46" s="99"/>
-      <c r="N46" s="99"/>
-      <c r="O46" s="99"/>
-      <c r="P46" s="100"/>
+      <c r="M46" s="81"/>
+      <c r="N46" s="81"/>
+      <c r="O46" s="81"/>
+      <c r="P46" s="82"/>
       <c r="Q46" s="23"/>
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
@@ -6326,15 +6326,15 @@
       <c r="B47" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="101" t="s">
+      <c r="C47" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="102"/>
-      <c r="E47" s="103"/>
-      <c r="F47" s="138">
+      <c r="D47" s="68"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="64">
         <v>1</v>
       </c>
-      <c r="G47" s="133" t="s">
+      <c r="G47" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H47" s="26" t="s">
@@ -6343,11 +6343,11 @@
       <c r="I47" s="23"/>
       <c r="J47" s="11"/>
       <c r="K47" s="32"/>
-      <c r="L47" s="116"/>
-      <c r="M47" s="108"/>
-      <c r="N47" s="108"/>
-      <c r="O47" s="108"/>
-      <c r="P47" s="109"/>
+      <c r="L47" s="83"/>
+      <c r="M47" s="84"/>
+      <c r="N47" s="84"/>
+      <c r="O47" s="84"/>
+      <c r="P47" s="85"/>
       <c r="Q47" s="23"/>
       <c r="R47" s="11"/>
       <c r="S47" s="11"/>
@@ -6360,15 +6360,15 @@
       <c r="B48" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="104" t="s">
+      <c r="C48" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="D48" s="105"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="134">
+      <c r="D48" s="71"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="60">
         <v>1</v>
       </c>
-      <c r="G48" s="136">
+      <c r="G48" s="62">
         <v>46023</v>
       </c>
       <c r="H48" s="29" t="s">
@@ -6394,15 +6394,15 @@
       <c r="B49" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="104" t="s">
+      <c r="C49" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="D49" s="105"/>
-      <c r="E49" s="106"/>
-      <c r="F49" s="134">
+      <c r="D49" s="71"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="60">
         <v>2</v>
       </c>
-      <c r="G49" s="135" t="s">
+      <c r="G49" s="61" t="s">
         <v>71</v>
       </c>
       <c r="H49" s="29" t="s">
@@ -6411,13 +6411,13 @@
       <c r="I49" s="23"/>
       <c r="J49" s="11"/>
       <c r="K49" s="32"/>
-      <c r="L49" s="112" t="s">
+      <c r="L49" s="86" t="s">
         <v>184</v>
       </c>
-      <c r="M49" s="113"/>
-      <c r="N49" s="113"/>
-      <c r="O49" s="113"/>
-      <c r="P49" s="114"/>
+      <c r="M49" s="87"/>
+      <c r="N49" s="87"/>
+      <c r="O49" s="87"/>
+      <c r="P49" s="88"/>
       <c r="Q49" s="23"/>
       <c r="R49" s="11"/>
       <c r="S49" s="11"/>
@@ -6430,15 +6430,15 @@
       <c r="B50" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="104" t="s">
+      <c r="C50" s="70" t="s">
         <v>185</v>
       </c>
-      <c r="D50" s="105"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="134">
+      <c r="D50" s="71"/>
+      <c r="E50" s="72"/>
+      <c r="F50" s="60">
         <v>1</v>
       </c>
-      <c r="G50" s="136">
+      <c r="G50" s="62">
         <v>46024</v>
       </c>
       <c r="H50" s="29" t="s">
@@ -6447,13 +6447,13 @@
       <c r="I50" s="23"/>
       <c r="J50" s="11"/>
       <c r="K50" s="32"/>
-      <c r="L50" s="115" t="s">
+      <c r="L50" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="M50" s="99"/>
-      <c r="N50" s="99"/>
-      <c r="O50" s="99"/>
-      <c r="P50" s="100"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
+      <c r="O50" s="81"/>
+      <c r="P50" s="82"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
@@ -6466,15 +6466,15 @@
       <c r="B51" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="104" t="s">
+      <c r="C51" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="D51" s="105"/>
-      <c r="E51" s="106"/>
-      <c r="F51" s="134">
+      <c r="D51" s="71"/>
+      <c r="E51" s="72"/>
+      <c r="F51" s="60">
         <v>1</v>
       </c>
-      <c r="G51" s="135" t="s">
+      <c r="G51" s="61" t="s">
         <v>130</v>
       </c>
       <c r="H51" s="29" t="s">
@@ -6483,11 +6483,11 @@
       <c r="I51" s="23"/>
       <c r="J51" s="11"/>
       <c r="K51" s="32"/>
-      <c r="L51" s="116"/>
-      <c r="M51" s="108"/>
-      <c r="N51" s="108"/>
-      <c r="O51" s="108"/>
-      <c r="P51" s="109"/>
+      <c r="L51" s="83"/>
+      <c r="M51" s="84"/>
+      <c r="N51" s="84"/>
+      <c r="O51" s="84"/>
+      <c r="P51" s="85"/>
       <c r="Q51" s="23"/>
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
@@ -6500,15 +6500,15 @@
       <c r="B52" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="101" t="s">
+      <c r="C52" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="102"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="133" t="s">
+      <c r="D52" s="68"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G52" s="137">
+      <c r="G52" s="63">
         <v>46025</v>
       </c>
       <c r="H52" s="26" t="s">
@@ -6534,15 +6534,15 @@
       <c r="B53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="101" t="s">
+      <c r="C53" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="102"/>
-      <c r="E53" s="103"/>
-      <c r="F53" s="138">
+      <c r="D53" s="68"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="64">
         <v>2</v>
       </c>
-      <c r="G53" s="133" t="s">
+      <c r="G53" s="59" t="s">
         <v>71</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -6568,15 +6568,15 @@
       <c r="B54" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="101" t="s">
+      <c r="C54" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="D54" s="102"/>
-      <c r="E54" s="103"/>
-      <c r="F54" s="138">
+      <c r="D54" s="68"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="64">
         <v>1</v>
       </c>
-      <c r="G54" s="133" t="s">
+      <c r="G54" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H54" s="26" t="s">
@@ -6602,15 +6602,15 @@
       <c r="B55" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="101" t="s">
+      <c r="C55" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="D55" s="102"/>
-      <c r="E55" s="103"/>
-      <c r="F55" s="138">
+      <c r="D55" s="68"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="64">
         <v>1</v>
       </c>
-      <c r="G55" s="137">
+      <c r="G55" s="63">
         <v>46025</v>
       </c>
       <c r="H55" s="26" t="s">
@@ -6636,15 +6636,15 @@
       <c r="B56" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="104" t="s">
+      <c r="C56" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="D56" s="105"/>
-      <c r="E56" s="106"/>
-      <c r="F56" s="134">
+      <c r="D56" s="71"/>
+      <c r="E56" s="72"/>
+      <c r="F56" s="60">
         <v>2</v>
       </c>
-      <c r="G56" s="136">
+      <c r="G56" s="62">
         <v>46054</v>
       </c>
       <c r="H56" s="29" t="s">
@@ -6670,15 +6670,15 @@
       <c r="B57" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="104" t="s">
+      <c r="C57" s="70" t="s">
         <v>199</v>
       </c>
-      <c r="D57" s="105"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="134">
+      <c r="D57" s="71"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="60">
         <v>1</v>
       </c>
-      <c r="G57" s="135" t="s">
+      <c r="G57" s="61" t="s">
         <v>130</v>
       </c>
       <c r="H57" s="29" t="s">
@@ -6698,14 +6698,14 @@
       <c r="T57" s="12"/>
     </row>
     <row r="58" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="122"/>
-      <c r="B58" s="123"/>
-      <c r="C58" s="123"/>
-      <c r="D58" s="123"/>
-      <c r="E58" s="123"/>
-      <c r="F58" s="123"/>
-      <c r="G58" s="123"/>
-      <c r="H58" s="124"/>
+      <c r="A58" s="89"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
+      <c r="H58" s="91"/>
       <c r="I58" s="23"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -6726,15 +6726,15 @@
       <c r="B59" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="104" t="s">
+      <c r="C59" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="D59" s="105"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="134">
+      <c r="D59" s="71"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="60">
         <v>1</v>
       </c>
-      <c r="G59" s="136">
+      <c r="G59" s="62">
         <v>46023</v>
       </c>
       <c r="H59" s="29" t="s">
@@ -6760,15 +6760,15 @@
       <c r="B60" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="134">
+      <c r="D60" s="71"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="60">
         <v>1</v>
       </c>
-      <c r="G60" s="135" t="s">
+      <c r="G60" s="61" t="s">
         <v>130</v>
       </c>
       <c r="H60" s="29" t="s">
@@ -6794,15 +6794,15 @@
       <c r="B61" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C61" s="101" t="s">
+      <c r="C61" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="D61" s="102"/>
-      <c r="E61" s="103"/>
-      <c r="F61" s="138">
+      <c r="D61" s="68"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="64">
         <v>2</v>
       </c>
-      <c r="G61" s="137">
+      <c r="G61" s="63">
         <v>46054</v>
       </c>
       <c r="H61" s="26" t="s">
@@ -6828,15 +6828,15 @@
       <c r="B62" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="101" t="s">
+      <c r="C62" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="D62" s="102"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="138">
+      <c r="D62" s="68"/>
+      <c r="E62" s="69"/>
+      <c r="F62" s="64">
         <v>1</v>
       </c>
-      <c r="G62" s="133" t="s">
+      <c r="G62" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H62" s="26" t="s">
@@ -6862,15 +6862,15 @@
       <c r="B63" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C63" s="101" t="s">
+      <c r="C63" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="D63" s="102"/>
-      <c r="E63" s="103"/>
-      <c r="F63" s="133" t="s">
+      <c r="D63" s="68"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G63" s="137">
+      <c r="G63" s="63">
         <v>46054</v>
       </c>
       <c r="H63" s="26" t="s">
@@ -6896,15 +6896,15 @@
       <c r="B64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="101" t="s">
+      <c r="C64" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="D64" s="102"/>
-      <c r="E64" s="103"/>
-      <c r="F64" s="133" t="s">
+      <c r="D64" s="68"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G64" s="133" t="s">
+      <c r="G64" s="59" t="s">
         <v>211</v>
       </c>
       <c r="H64" s="26" t="s">
@@ -6930,15 +6930,15 @@
       <c r="B65" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C65" s="101" t="s">
+      <c r="C65" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="D65" s="102"/>
-      <c r="E65" s="103"/>
-      <c r="F65" s="138">
+      <c r="D65" s="68"/>
+      <c r="E65" s="69"/>
+      <c r="F65" s="64">
         <v>2</v>
       </c>
-      <c r="G65" s="137">
+      <c r="G65" s="63">
         <v>46082</v>
       </c>
       <c r="H65" s="26" t="s">
@@ -6964,15 +6964,15 @@
       <c r="B66" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="101" t="s">
+      <c r="C66" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="D66" s="102"/>
-      <c r="E66" s="103"/>
-      <c r="F66" s="138">
+      <c r="D66" s="68"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="64">
         <v>2</v>
       </c>
-      <c r="G66" s="133" t="s">
+      <c r="G66" s="59" t="s">
         <v>71</v>
       </c>
       <c r="H66" s="26" t="s">
@@ -6998,15 +6998,15 @@
       <c r="B67" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C67" s="104" t="s">
+      <c r="C67" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="105"/>
-      <c r="E67" s="106"/>
-      <c r="F67" s="134">
+      <c r="D67" s="71"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="60">
         <v>2</v>
       </c>
-      <c r="G67" s="135" t="s">
+      <c r="G67" s="61" t="s">
         <v>81</v>
       </c>
       <c r="H67" s="29" t="s">
@@ -7032,15 +7032,15 @@
       <c r="B68" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C68" s="104" t="s">
+      <c r="C68" s="70" t="s">
         <v>219</v>
       </c>
-      <c r="D68" s="105"/>
-      <c r="E68" s="106"/>
-      <c r="F68" s="134">
+      <c r="D68" s="71"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="60">
         <v>1</v>
       </c>
-      <c r="G68" s="136">
+      <c r="G68" s="62">
         <v>46055</v>
       </c>
       <c r="H68" s="29" t="s">
@@ -7066,15 +7066,15 @@
       <c r="B69" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="104" t="s">
+      <c r="C69" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="D69" s="105"/>
-      <c r="E69" s="106"/>
-      <c r="F69" s="134">
+      <c r="D69" s="71"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="60">
         <v>1</v>
       </c>
-      <c r="G69" s="136">
+      <c r="G69" s="62">
         <v>46024</v>
       </c>
       <c r="H69" s="29" t="s">
@@ -7100,15 +7100,15 @@
       <c r="B70" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C70" s="104" t="s">
+      <c r="C70" s="70" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="105"/>
-      <c r="E70" s="106"/>
-      <c r="F70" s="135" t="s">
+      <c r="D70" s="71"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G70" s="136">
+      <c r="G70" s="62">
         <v>46023</v>
       </c>
       <c r="H70" s="29" t="s">
@@ -7134,15 +7134,15 @@
       <c r="B71" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="104" t="s">
+      <c r="C71" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="D71" s="105"/>
-      <c r="E71" s="106"/>
-      <c r="F71" s="135" t="s">
+      <c r="D71" s="71"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G71" s="136">
+      <c r="G71" s="62">
         <v>46054</v>
       </c>
       <c r="H71" s="29" t="s">
@@ -7168,15 +7168,15 @@
       <c r="B72" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="104" t="s">
+      <c r="C72" s="70" t="s">
         <v>226</v>
       </c>
-      <c r="D72" s="105"/>
-      <c r="E72" s="106"/>
-      <c r="F72" s="134">
+      <c r="D72" s="71"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="60">
         <v>1</v>
       </c>
-      <c r="G72" s="135" t="s">
+      <c r="G72" s="61" t="s">
         <v>55</v>
       </c>
       <c r="H72" s="29" t="s">
@@ -7202,15 +7202,15 @@
       <c r="B73" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C73" s="101" t="s">
+      <c r="C73" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="D73" s="102"/>
-      <c r="E73" s="103"/>
-      <c r="F73" s="133" t="s">
+      <c r="D73" s="68"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G73" s="137">
+      <c r="G73" s="63">
         <v>46082</v>
       </c>
       <c r="H73" s="26" t="s">
@@ -7236,15 +7236,15 @@
       <c r="B74" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C74" s="101" t="s">
+      <c r="C74" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="D74" s="102"/>
-      <c r="E74" s="103"/>
-      <c r="F74" s="133" t="s">
+      <c r="D74" s="68"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="G74" s="133" t="s">
+      <c r="G74" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H74" s="26" t="s">
@@ -7270,15 +7270,15 @@
       <c r="B75" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="101" t="s">
+      <c r="C75" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="D75" s="102"/>
-      <c r="E75" s="103"/>
-      <c r="F75" s="138">
+      <c r="D75" s="68"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="64">
         <v>1</v>
       </c>
-      <c r="G75" s="133" t="s">
+      <c r="G75" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H75" s="26" t="s">
@@ -7304,15 +7304,15 @@
       <c r="B76" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C76" s="101" t="s">
+      <c r="C76" s="67" t="s">
         <v>234</v>
       </c>
-      <c r="D76" s="102"/>
-      <c r="E76" s="103"/>
-      <c r="F76" s="138">
+      <c r="D76" s="68"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="64">
         <v>2</v>
       </c>
-      <c r="G76" s="133" t="s">
+      <c r="G76" s="59" t="s">
         <v>81</v>
       </c>
       <c r="H76" s="26" t="s">
@@ -7338,15 +7338,15 @@
       <c r="B77" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="101" t="s">
+      <c r="C77" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="D77" s="102"/>
-      <c r="E77" s="103"/>
-      <c r="F77" s="138">
+      <c r="D77" s="68"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="64">
         <v>2</v>
       </c>
-      <c r="G77" s="133" t="s">
+      <c r="G77" s="59" t="s">
         <v>237</v>
       </c>
       <c r="H77" s="26" t="s">
@@ -7372,15 +7372,15 @@
       <c r="B78" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C78" s="101" t="s">
+      <c r="C78" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="D78" s="102"/>
-      <c r="E78" s="103"/>
-      <c r="F78" s="138">
+      <c r="D78" s="68"/>
+      <c r="E78" s="69"/>
+      <c r="F78" s="64">
         <v>1</v>
       </c>
-      <c r="G78" s="137">
+      <c r="G78" s="63">
         <v>46024</v>
       </c>
       <c r="H78" s="26" t="s">
@@ -7406,15 +7406,15 @@
       <c r="B79" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C79" s="104" t="s">
+      <c r="C79" s="70" t="s">
         <v>239</v>
       </c>
-      <c r="D79" s="105"/>
-      <c r="E79" s="106"/>
-      <c r="F79" s="134">
+      <c r="D79" s="71"/>
+      <c r="E79" s="72"/>
+      <c r="F79" s="60">
         <v>2</v>
       </c>
-      <c r="G79" s="136">
+      <c r="G79" s="62">
         <v>46082</v>
       </c>
       <c r="H79" s="29" t="s">
@@ -7440,15 +7440,15 @@
       <c r="B80" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C80" s="104" t="s">
+      <c r="C80" s="70" t="s">
         <v>241</v>
       </c>
-      <c r="D80" s="105"/>
-      <c r="E80" s="106"/>
-      <c r="F80" s="134">
+      <c r="D80" s="71"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="60">
         <v>2</v>
       </c>
-      <c r="G80" s="135" t="s">
+      <c r="G80" s="61" t="s">
         <v>144</v>
       </c>
       <c r="H80" s="29" t="s">
@@ -7474,15 +7474,15 @@
       <c r="B81" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C81" s="104" t="s">
+      <c r="C81" s="70" t="s">
         <v>243</v>
       </c>
-      <c r="D81" s="105"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="134">
+      <c r="D81" s="71"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="60">
         <v>2</v>
       </c>
-      <c r="G81" s="135" t="s">
+      <c r="G81" s="61" t="s">
         <v>244</v>
       </c>
       <c r="H81" s="29" t="s">
@@ -7508,15 +7508,15 @@
       <c r="B82" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="C82" s="129" t="s">
+      <c r="C82" s="73" t="s">
         <v>246</v>
       </c>
-      <c r="D82" s="130"/>
-      <c r="E82" s="131"/>
-      <c r="F82" s="139" t="s">
+      <c r="D82" s="74"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="G82" s="140">
+      <c r="G82" s="66">
         <v>46023</v>
       </c>
       <c r="H82" s="35" t="s">
@@ -7537,29 +7537,98 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="A5:T6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="J7:Q7"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="L24:P25"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M28:P29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="M30:P31"/>
+    <mergeCell ref="L33:P33"/>
+    <mergeCell ref="L34:P35"/>
+    <mergeCell ref="L37:P37"/>
+    <mergeCell ref="L38:P39"/>
+    <mergeCell ref="L41:P41"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="L42:P43"/>
+    <mergeCell ref="L45:P45"/>
+    <mergeCell ref="L46:P47"/>
+    <mergeCell ref="L49:P49"/>
+    <mergeCell ref="L50:P51"/>
+    <mergeCell ref="A58:H58"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C2:F2"/>
@@ -7584,98 +7653,29 @@
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="L42:P43"/>
-    <mergeCell ref="L45:P45"/>
-    <mergeCell ref="L46:P47"/>
-    <mergeCell ref="L49:P49"/>
-    <mergeCell ref="L50:P51"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="L33:P33"/>
-    <mergeCell ref="L34:P35"/>
-    <mergeCell ref="L37:P37"/>
-    <mergeCell ref="L38:P39"/>
-    <mergeCell ref="L41:P41"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="L24:P25"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M28:P29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="M30:P31"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="A5:T6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="J7:Q7"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
   </mergeCells>
   <dataValidations count="13">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F32 F34:F57 F59:F82" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -7736,11 +7736,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="140" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
     </row>
     <row r="2" spans="1:3" ht="15.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
